--- a/despiece-closet.xlsx
+++ b/despiece-closet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7e4bb88fb3ffb2f3/Desktop/proyecto_terraza/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="11_1010BCAFECFCD321D5BDC7783D3CA87A8D0287D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E2B24E1-8AA9-4D62-B084-21B67B0E01C0}"/>
+  <xr:revisionPtr revIDLastSave="228" documentId="11_1010BCAFECFCD321D5BDC7783D3CA87A8D0287D7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5348D65A-8D40-4341-AEFE-74741A86B40C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="299">
   <si>
     <t>Clóset principal 195: despiece independiente</t>
   </si>
@@ -280,9 +280,6 @@
     <t>Pendiente plantilla</t>
   </si>
   <si>
-    <t>PROVISIONAL para corte: 2175 × 975, solape 30. Altura = hueco bajo el listón (2340−115) menos 50 mm del sistema. Sin perfil vertical en esta propuesta basada en el clóset del usuario. Confirmar taladros, altura, canto y suspensión. Tope conserva desfase de 50 mm entre hojas.</t>
-  </si>
-  <si>
     <t>C3-024</t>
   </si>
   <si>
@@ -316,9 +313,6 @@
     <t>Veta horizontal: frente de 824 de ancho, queda detrás de las hojas.</t>
   </si>
   <si>
-    <t>Cortar después de confirmar el kit Peralma (altura de hoja y plantilla).</t>
-  </si>
-  <si>
     <t>Supuestos por confirmar en la sucursal: Q2 cambia la medida que se pide; Q3 y Q4 marcan qué piezas pueden rechazar.</t>
   </si>
   <si>
@@ -838,12 +832,6 @@
     <t>Sucursal Madecentro</t>
   </si>
   <si>
-    <t>Confirmar con el kit Peralma FSCPCM20 la altura de hoja, la plantilla y la carga (hojas de ≈21,3 kg; el kit indica 30 kg: ¿por hoja o por kit?). Verificar si el tope amortiguado viene en el kit.</t>
-  </si>
-  <si>
-    <t>No cortar C3-023</t>
-  </si>
-  <si>
     <t>Proveedor del sistema</t>
   </si>
   <si>
@@ -926,6 +914,27 @@
   </si>
   <si>
     <t>Geometría del diseño.</t>
+  </si>
+  <si>
+    <t>Pedida 20 mm más alta (2195 en vez de 2175): en el armado, con el riel y los carros puestos, recortar el borde superior —tapado por la solapa— hasta que la guía inferior sujete la hoja. Nunca debe quedar corta.</t>
+  </si>
+  <si>
+    <t>Confirmar con el kit Peralma FSCPCM20 la carga (hojas de ≈21,3 kg; el kit indica 30 kg: ¿por hoja o por kit?) y si trae el tope amortiguado. La altura final de las hojas se ajusta en el armado.</t>
+  </si>
+  <si>
+    <t>Compra del kit; recorte de C3-023 en el armado</t>
+  </si>
+  <si>
+    <t>Hojas con sobremedida</t>
+  </si>
+  <si>
+    <t>Las hojas se piden de 2195 × 975 (20 mm más altas) y se recortan arriba en el armado, con el riel y los carros puestos, hasta que la guía inferior sujete la hoja. El borde recortado queda tapado por la solapa. La medida terminada de diseño sigue siendo 2175.</t>
+  </si>
+  <si>
+    <t>Decisión del usuario 27/10/2026</t>
+  </si>
+  <si>
+    <t>Medida terminada 2175 × 975, solape 30. Se pide de 2195 (20 mm más alta) y se recorta arriba en el armado, con el riel y los carros puestos, hasta que la guía inferior sujete la hoja; el borde recortado queda tapado por la solapa. Altura = hueco bajo el listón (2340−115) menos 50 mm del sistema. Sin perfil vertical, como el clóset del usuario. Tope conserva desfase de 50 mm entre hojas.</t>
   </si>
 </sst>
 </file>
@@ -1142,15 +1151,15 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1235,6 +1244,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2786,19 +2799,19 @@
       <c r="O29" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="P29" s="4" t="s">
-        <v>80</v>
+      <c r="P29" s="13" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D30" s="1">
         <v>1</v>
@@ -2840,7 +2853,7 @@
         <v>25</v>
       </c>
       <c r="P30" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2865,7 +2878,7 @@
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D32" s="1">
         <f>SUM(D7:D30)</f>
@@ -2874,7 +2887,7 @@
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H32" s="5">
         <f>SUM(H7:H30)</f>
@@ -2891,7 +2904,7 @@
     </row>
     <row r="33" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -2955,32 +2968,32 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="S1" s="14" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="P2" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="P2" s="17" t="s">
-        <v>89</v>
-      </c>
       <c r="Q2" s="18" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="S2" s="14" t="s">
         <v>19</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="P3" s="17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="Q3" s="26">
         <v>100</v>
@@ -2989,15 +3002,15 @@
         <v>56</v>
       </c>
       <c r="T3" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="Q4" s="26">
         <v>250</v>
@@ -3006,12 +3019,12 @@
         <v>76</v>
       </c>
       <c r="T4" s="14" t="s">
-        <v>92</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="P5" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="26.4" x14ac:dyDescent="0.25">
@@ -3019,43 +3032,43 @@
         <v>3</v>
       </c>
       <c r="B6" s="19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C6" s="19" t="s">
         <v>5</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E6" s="19" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="19" t="s">
+      <c r="I6" s="19" t="s">
         <v>97</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="J6" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="19" t="s">
+      <c r="K6" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="J6" s="19" t="s">
+      <c r="L6" s="19" t="s">
         <v>100</v>
       </c>
-      <c r="K6" s="19" t="s">
+      <c r="M6" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="N6" s="19" t="s">
         <v>102</v>
-      </c>
-      <c r="M6" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="N6" s="19" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -4334,7 +4347,7 @@
         <v>Si no la cantean: cortar a 479,1 × 79,1 y cantear en el armado.</v>
       </c>
     </row>
-    <row r="29" spans="1:14" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A29" s="20" t="str">
         <f>Despiece!A29</f>
         <v>C3-023</v>
@@ -4356,8 +4369,8 @@
         <v>2</v>
       </c>
       <c r="F29" s="31">
-        <f>IF($Q$2="NO",ROUND(Despiece!M29,2),Despiece!E29)</f>
-        <v>2175</v>
+        <f>IF($Q$2="NO",ROUND(Despiece!M29,2),Despiece!E29)+20</f>
+        <v>2195</v>
       </c>
       <c r="G29" s="31">
         <f>IF($Q$2="NO",ROUND(Despiece!N29,2),Despiece!F29)</f>
@@ -4389,7 +4402,7 @@
       </c>
       <c r="N29" s="22" t="str">
         <f>IF(LEN(TRIM(IF($L29="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M29,2)&amp;" × "&amp;ROUND(Despiece!N29,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A29,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L29="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M29,2)&amp;" × "&amp;ROUND(Despiece!N29,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A29,$S$2:$T$40,2,FALSE),"")))</f>
-        <v>Cortar después de confirmar el kit Peralma (altura de hoja y plantilla).</v>
+        <v>Pedida 20 mm más alta (2195 en vez de 2175): en el armado, con el riel y los carros puestos, recortar el borde superior —tapado por la solapa— hasta que la guía inferior sujete la hoja. Nunca debe quedar corta.</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -4452,20 +4465,20 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="C32" s="16" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="23"/>
       <c r="F32" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C33" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D33" s="23"/>
       <c r="E33" s="23"/>
@@ -4480,7 +4493,7 @@
     </row>
     <row r="34" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C34" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="23"/>
@@ -4495,7 +4508,7 @@
     </row>
     <row r="35" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C35" s="16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D35" s="23"/>
       <c r="E35" s="23"/>
@@ -4510,20 +4523,20 @@
     </row>
     <row r="37" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C37" s="16" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D37" s="23"/>
       <c r="E37" s="23"/>
       <c r="F37" s="16" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="38" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C38" s="14" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F38" s="27">
         <f>SUMPRODUCT(Despiece!$D$7:$D$30,(Despiece!$I$7:$I$30="2")+(Despiece!$J$7:$J$30="2")+(Despiece!$K$7:$K$30="2")+(Despiece!$L$7:$L$30="2"),--($L$7:$L$30="Pequeña"))</f>
@@ -4536,7 +4549,7 @@
     </row>
     <row r="39" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C39" s="14" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F39" s="28">
         <f>G33</f>
@@ -4549,7 +4562,7 @@
     </row>
     <row r="40" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C40" s="14" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F40" s="29">
         <v>0.1</v>
@@ -4560,7 +4573,7 @@
     </row>
     <row r="41" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C41" s="14" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F41" s="30">
         <v>0.2</v>
@@ -4571,7 +4584,7 @@
     </row>
     <row r="42" spans="3:14" x14ac:dyDescent="0.25">
       <c r="C42" s="16" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D42" s="23"/>
       <c r="E42" s="23"/>
@@ -4585,31 +4598,31 @@
       </c>
     </row>
     <row r="43" spans="3:14" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C43" s="38" t="s">
-        <v>242</v>
-      </c>
-      <c r="D43" s="39"/>
-      <c r="E43" s="39"/>
-      <c r="F43" s="39"/>
-      <c r="G43" s="39"/>
-      <c r="H43" s="39"/>
-      <c r="I43" s="39"/>
-      <c r="J43" s="39"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="39"/>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
+      <c r="C43" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" s="40"/>
+      <c r="E43" s="40"/>
+      <c r="F43" s="40"/>
+      <c r="G43" s="40"/>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="40"/>
+      <c r="K43" s="40"/>
+      <c r="L43" s="40"/>
+      <c r="M43" s="40"/>
+      <c r="N43" s="40"/>
     </row>
     <row r="44" spans="3:14" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F44" s="32"/>
       <c r="G44" s="32"/>
     </row>
     <row r="45" spans="3:14" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C45" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="F45" s="32">
         <v>0</v>
@@ -4620,7 +4633,7 @@
     </row>
     <row r="46" spans="3:14" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="33" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D46" s="33"/>
       <c r="E46" s="33"/>
@@ -4634,20 +4647,20 @@
       </c>
     </row>
     <row r="47" spans="3:14" ht="49.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C47" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="D47" s="39"/>
-      <c r="E47" s="39"/>
-      <c r="F47" s="39"/>
-      <c r="G47" s="39"/>
-      <c r="H47" s="39"/>
-      <c r="I47" s="39"/>
-      <c r="J47" s="39"/>
-      <c r="K47" s="39"/>
-      <c r="L47" s="39"/>
-      <c r="M47" s="39"/>
-      <c r="N47" s="39"/>
+      <c r="C47" s="41" t="s">
+        <v>244</v>
+      </c>
+      <c r="D47" s="40"/>
+      <c r="E47" s="40"/>
+      <c r="F47" s="40"/>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="40"/>
+      <c r="N47" s="40"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4692,7 +4705,7 @@
     </row>
     <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -4706,7 +4719,7 @@
     </row>
     <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -4720,7 +4733,7 @@
     </row>
     <row r="4" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -4746,46 +4759,46 @@
     </row>
     <row r="6" spans="1:10" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="I6" s="1"/>
       <c r="J6" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C7" s="1">
         <v>5</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E7" s="9">
         <v>365872</v>
@@ -4795,29 +4808,29 @@
         <v>1829360</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="13" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C8" s="1">
         <f>Cantos!H7</f>
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E8" s="9">
         <v>531600</v>
@@ -4827,29 +4840,29 @@
         <v>531600</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="I8" s="1"/>
       <c r="J8" s="13" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C9" s="1">
         <f>Cantos!H8</f>
         <v>1</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E9" s="9">
         <v>285600</v>
@@ -4859,28 +4872,28 @@
         <v>285600</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="I9" s="1"/>
       <c r="J9" s="13" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C10" s="1">
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="E10" s="9">
         <v>11287</v>
@@ -4890,28 +4903,28 @@
         <v>33861</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="I10" s="12"/>
       <c r="J10" s="13" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C11" s="1">
         <v>1</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E11" s="9">
         <v>12730</v>
@@ -4921,28 +4934,28 @@
         <v>12730</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I11" s="1"/>
       <c r="J11" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C12" s="1">
         <v>1</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E12" s="9">
         <v>33278</v>
@@ -4952,28 +4965,28 @@
         <v>33278</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I12" s="1"/>
       <c r="J12" s="4" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C13" s="1">
         <v>2</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E13" s="9">
         <v>2743</v>
@@ -4983,26 +4996,26 @@
         <v>5486</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I13" s="1"/>
       <c r="J13" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="str">
@@ -5010,28 +5023,28 @@
         <v>Por cotizar</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I14" s="1"/>
       <c r="J14" s="4" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C15" s="1">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E15" s="9"/>
       <c r="F15" s="9" t="str">
@@ -5039,28 +5052,28 @@
         <v>Por cotizar</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="I15" s="1"/>
       <c r="J15" s="4" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C16" s="1">
         <v>6</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="9" t="str">
@@ -5068,28 +5081,28 @@
         <v>Por cotizar</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I16" s="1"/>
       <c r="J16" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C17" s="1">
         <v>6</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9" t="str">
@@ -5097,28 +5110,28 @@
         <v>Por cotizar</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="I17" s="1"/>
       <c r="J17" s="4" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C18" s="1">
         <v>1</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E18" s="9"/>
       <c r="F18" s="9" t="str">
@@ -5126,28 +5139,28 @@
         <v>Por cotizar</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I18" s="1"/>
       <c r="J18" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C19" s="1">
         <v>1</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E19" s="9"/>
       <c r="F19" s="9" t="str">
@@ -5155,28 +5168,28 @@
         <v>Por cotizar</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="I19" s="1"/>
       <c r="J19" s="4" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C20" s="1">
         <v>1</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E20" s="9"/>
       <c r="F20" s="9" t="str">
@@ -5184,28 +5197,28 @@
         <v>Por cotizar</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="I20" s="1"/>
       <c r="J20" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C21" s="1">
         <v>1</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E21" s="9"/>
       <c r="F21" s="9" t="str">
@@ -5213,19 +5226,19 @@
         <v>Por cotizar</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I21" s="1"/>
       <c r="J21" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
@@ -5236,8 +5249,8 @@
         <v>2731915</v>
       </c>
       <c r="G22" s="10"/>
-      <c r="H22" s="41" t="s">
-        <v>294</v>
+      <c r="H22" s="38" t="s">
+        <v>290</v>
       </c>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -5299,7 +5312,7 @@
     </row>
     <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -5308,7 +5321,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I2" s="1">
         <v>0.05</v>
@@ -5316,7 +5329,7 @@
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -5351,37 +5364,37 @@
     </row>
     <row r="6" spans="1:9" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="I6" s="1"/>
     </row>
     <row r="7" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C7" s="8">
         <f>SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="2")+(Despiece!$J$7:$J$30="2"))/1000+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="2")+(Despiece!$L$7:$L$30="2"))/1000</f>
@@ -5410,10 +5423,10 @@
     </row>
     <row r="8" spans="1:9" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C8" s="8">
         <f>SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="0.45")+(Despiece!$J$7:$J$30="0.45"))/1000+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="0.45")+(Despiece!$L$7:$L$30="0.45"))/1000</f>
@@ -5453,7 +5466,7 @@
     </row>
     <row r="10" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -5504,29 +5517,29 @@
   <sheetData>
     <row r="2" spans="1:5" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="B6" s="35" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="B6" s="35" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="35" t="s">
+      <c r="E6" s="35" t="s">
         <v>255</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>256</v>
-      </c>
-      <c r="E6" s="35" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5534,16 +5547,16 @@
         <v>1</v>
       </c>
       <c r="B7" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="D7" s="37" t="s">
         <v>258</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="E7" s="37" t="s">
         <v>259</v>
-      </c>
-      <c r="D7" s="37" t="s">
-        <v>260</v>
-      </c>
-      <c r="E7" s="37" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5551,16 +5564,16 @@
         <v>2</v>
       </c>
       <c r="B8" s="37" t="s">
+        <v>260</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>261</v>
+      </c>
+      <c r="D8" s="37" t="s">
         <v>262</v>
       </c>
-      <c r="C8" s="37" t="s">
+      <c r="E8" s="37" t="s">
         <v>263</v>
-      </c>
-      <c r="D8" s="37" t="s">
-        <v>264</v>
-      </c>
-      <c r="E8" s="37" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5568,16 +5581,16 @@
         <v>3</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="D9" s="37" t="s">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5585,16 +5598,16 @@
         <v>4</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
@@ -5602,16 +5615,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="D11" s="37" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5619,16 +5632,16 @@
         <v>6</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C12" s="37" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5636,16 +5649,16 @@
         <v>7</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="26.4" x14ac:dyDescent="0.25">
@@ -5653,16 +5666,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C14" s="37" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="E14" s="37" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -5672,7 +5685,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{056A28ED-57E4-401D-9DBD-33391A6C79EA}">
-  <dimension ref="A2:C15"/>
+  <dimension ref="A2:C16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.77734375" customWidth="1"/>
@@ -5682,122 +5695,133 @@
   <sheetData>
     <row r="2" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A2" s="15" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>206</v>
+      </c>
+      <c r="C7" s="37" t="s">
         <v>207</v>
-      </c>
-      <c r="B7" s="37" t="s">
-        <v>208</v>
-      </c>
-      <c r="C7" s="37" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A8" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8" s="37" t="s">
         <v>210</v>
-      </c>
-      <c r="B8" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="C8" s="37" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="37" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>212</v>
+      </c>
+      <c r="C9" s="37" t="s">
         <v>213</v>
-      </c>
-      <c r="B9" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="C9" s="37" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A10" s="37" t="s">
+        <v>214</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="37" t="s">
         <v>216</v>
-      </c>
-      <c r="B10" s="37" t="s">
-        <v>217</v>
-      </c>
-      <c r="C10" s="37" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A11" s="37" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="C11" s="37" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A12" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="37" t="s">
         <v>221</v>
-      </c>
-      <c r="B12" s="37" t="s">
-        <v>222</v>
-      </c>
-      <c r="C12" s="37" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A13" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="C13" s="37" t="s">
         <v>224</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>225</v>
-      </c>
-      <c r="C13" s="37" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A14" s="37" t="s">
+        <v>226</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="C14" s="37" t="s">
         <v>228</v>
-      </c>
-      <c r="B14" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="C14" s="37" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A15" s="37" t="s">
+        <v>230</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="C15" s="37" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="37" t="s">
-        <v>233</v>
-      </c>
-      <c r="C15" s="37" t="s">
-        <v>234</v>
+    </row>
+    <row r="16" spans="1:3" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A16" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/despiece-closet.xlsx
+++ b/despiece-closet.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Despiece" sheetId="1" r:id="R98819bf0dfc14dc1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedido de corte" sheetId="7" r:id="R09a062646b384ceb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras" sheetId="3" r:id="R5fa781cf36194761"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantos" sheetId="2" r:id="R57b09103133f4959"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes" sheetId="8" r:id="Rb3da0e3b40104ad7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisiones" sheetId="9" r:id="Re239f97c51894319"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Despiece" sheetId="1" r:id="R2fe18918cc63435f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedido de corte" sheetId="7" r:id="R1a91d0368c7947c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compras" sheetId="3" r:id="R36504e695be14856"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cantos" sheetId="2" r:id="R8aa14019c69248fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pendientes" sheetId="8" r:id="R5b4b21041ca04f78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decisiones" sheetId="9" r:id="R1c8b9d0bfe4547af"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,9 +21,6 @@
     <x:t xml:space="preserve">Cuerpo 195 × 56 × 238 cm; 58,5 cm hasta las manijas. RH15 como cocina. Despiece exclusivo del clóset.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">E/F: medidas terminadas y veta en E. I/J paralelos a E, K/L paralelos a F. Cortes teóricos sin sierra ni refilado.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ID</x:t>
   </x:si>
   <x:si>
@@ -117,15 +114,6 @@
     <x:t xml:space="preserve">Tapa de 505 mm: llega hasta el listón de pino 4×4 cm (P3-01), que sostiene el riel. Se une a laterales y divisor; el listón queda a ras de su cara superior.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">C3-005</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fondo RH15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Panel trasero del mismo RH15 y acabado. Útil de colgado hasta la hoja trasera: 485 mm.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">C3-006</x:t>
   </x:si>
   <x:si>
@@ -162,9 +150,6 @@
     <x:t xml:space="preserve">C3-010</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">C3-011</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">C3-012</x:t>
   </x:si>
   <x:si>
@@ -258,15 +243,6 @@
     <x:t xml:space="preserve">Cubre el frente superior (riel y borde alto de las hojas), como en el clóset real: 12 cm de alto, sobresale 15 mm delante del cuerpo de 56 cm. Se fija a los cantos delanteros de los laterales y a dos tacos de pino de 15 mm (sobrantes del listón) atornillados al frente del listón. Canto rígido abajo y en los extremos; el borde alto va contra el cielo raso.</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">TOTAL RH15</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Área neta</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Listón de pino (bastidor del riel) fuera de este total: ver hoja Compras.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Observaciones fijas por pieza</x:t>
   </x:si>
   <x:si>
@@ -333,324 +309,264 @@
     <x:t xml:space="preserve">Observaciones</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Metros netos de canto</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Normal</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pequeña</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rígido 2 mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Flexible 0,45 mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Piezas (unidades)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Canto para acabado manual · previsión sujeta a la entrega</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Bordes a cantear a mano</x:t>
+    <x:t xml:space="preserve">Clóset compacto: compras independientes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Presupuesto parcial del clóset principal. Precios de referencia; materiales independientes de la cocina.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Referencia</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Uso</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cantidad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Unidad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Precio COP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Importe COP</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Detalle</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Fuente / fecha</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">RH15 Cartagena</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tablero 2440 × 2150</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lámina</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Misma referencia cocina</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">despiece-cocina.xlsx, Compras; precio de referencia 27/10/2026.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Canto rígido Cartagena</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rollo 19 × 2 mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">rollo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Referencia cocina</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cantidad exclusiva de este clóset, calculada en Cantos. No se han descontado sobrantes de otros muebles. Para acabado manual: ver «Metros faltantes por comprar» al final de Pedido de corte; descontar material ya disponible. Precio por metro suelto y pegante por cotizar.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">despiece-cocina.xlsx, Compras.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Canto flexible Cartagena</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Rollo 19 × 0,45 mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HRE320-45</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Riel lateral 450 mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">par</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Precio aportado</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Vano 830 − 27 = caja 803 × 450. Los 45 kg nominales del par no certifican la caja ni la carga útil. Incluye 12 tornillos de 12 mm por par. Confirmar uniones.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Usuario; ficha HRE320/330 rev. 15/05/25.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">FSCPCM20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kit Peralma para dos hojas</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">kit</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Candidato</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Kit publicado: 4 rodamientos, 1 guía, 1 tope y tornillos. Identificar si coinciden con la guía y el amortiguador descritos por el usuario, antes de añadir accesorios. Cada hoja RH pesa 21,3 kg sin herrajes (10,05 kg/m², dato de Madecentro); el kit indica 30 kg: preguntar si es por hoja o por kit de dos.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://madecentro.com/products/kit-de-accesorios-para-sistema-colgante; precio aportado por usuario.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">PERALMA50B · 2 m</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Riel colgante superior para 2 hojas</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">barra</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Barra 2 m para recorrido 1920 mm. Referencia real: zona de 70 mm de fondo, hojas entre 500 y 550 mm, cuerpo hasta 560. El riel se atornilla al listón de pino del bastidor (no a la tapa). Guía inferior sin apoyo de peso; no hay riel inferior de carga. Confirmar sección y taladros del sistema.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">https://madecentro.com/products/sistema-corredizo-colgate-x-3mtr</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">HMA310-02</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Manija tubular CC96 mm</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">unidad</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Elegida</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Una manija vertical en el extremo exterior de cada hoja.35 mm de saliente: fondo máximo 585 mm. Dos centros 96 mm; largo representado 119 mm. Las manijas no sustituyen una certificación de rigidez del tablero.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Usuario: $2.743/unidad. https://madecentro.com/products/hma310-02-manija-310-acero-inox-cc-96-mm-rectangular-alta</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Verificar con FSCPCM20</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tope plástico amortiguado</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">conjunto</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Verificar incluido</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Detrás de la hoja exterior, conserva 50 mm de desfase y evita invertir el orden de hojas. Cota de pérdida de recorrido aportada por el usuario. Verificar si viene en el kit; no duplicar compra. La guía inferior tampoco se compra dos veces.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Descripción y fotos del clóset real del usuario; referencia comercial pendiente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Por elegir</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Barras para colgar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">tramo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Cotizar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Una ilustrada 810 mm y dos 1055 mm. Barra baja derecha desmontable. Medidas de corte reales según soportes elegidos.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Modelo; no representa una referencia comercial confirmada.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Soportes de barra</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dos por barra. Fijación y carga para RH15 por confirmar.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Montaje pendiente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Por dimensionar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Apoyos de base</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Dos bajo cada lateral/divisor. El modelo dibuja 20 mm de apoyo y base total 100 mm; producto y regulación por elegir.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Geometría propuesta.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Uniones y anclajes</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">lote</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Montaje y sustrato real.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Pino · por cotizar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Listón 4×4 cm · bastidor del riel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">listón</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Listón de pino de 4×4 cm que va de lateral a lateral: 1920 mm libres más el encaje en cada lateral (máx. 7 mm por lado). Pedir de 2,0 m o más, recto, seco y sin nudos grandes; sobra para 2 tacos de 15 mm. Va encajonado y atornillado a los laterales; el riel (50 mm) se atornilla a su cara inferior y sobresale ~5 mm por lado. El clóset real usa 7×3 cm; se cambió a 4×4 por disponibilidad. Confirmar rebaje y tornillos con el instalador.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Descripción del clóset real del usuario, 27/10/2026; precio pendiente.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tornillos del bastidor y del riel</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tornillos para madera y aglomerado en cada extremo del listón y para el riel; el kit del sistema puede traer los suyos. Escuadras solo si el rebaje en los laterales queda corto.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Por cotizar</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Corte, canteado e instalación</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">servicio</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Proveedor.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">SUBTOTAL PARCIAL</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Incluye 2 manijas por $5.486. Quedan listón de pino, tornillos, barras, apoyos, uniones, anclajes y servicios. Verificar accesorios incluidos. No hay PERALM93 presupuestado en este diseño.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Clóset compacto: cantos exclusivos</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Reserva/borde m</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Tipo</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">Aplicación</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Metros netos</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Desperdicio por borde a mano (m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Margen de seguridad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Estimado con desperdicio y reserva (m)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Previsión para las piezas pequeñas, no garantía de cuáles canteará Madecentro. Incluye 10 cm extra por borde y 20 % de reserva; ambos valores son editables. Al recibir las piezas, ajustar el objetivo si faltan otros bordes o si el proveedor canteó parte de ellos.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Objetivo revisado con reserva (m; opcional)</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Metros ya disponibles para cantear en casa</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Metros faltantes por comprar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dejar el objetivo revisado vacío para usar el estimado. Si ya hay canto comprado o sobrante de rollos, anotarlo en metros disponibles. No sumar este material dos veces al presupuesto. Precio por metro suelto y pegante por cotizar con el proveedor.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Clóset compacto: compras independientes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Presupuesto parcial del clóset principal. Precios de referencia; materiales independientes de la cocina.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cinco láminas es un encaje encontrado sin rotar por veta; no representa un mínimo demostrado.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Referencia</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Uso</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cantidad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Unidad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Precio COP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Importe COP</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Detalle</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Fuente / fecha</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">RH15 Cartagena</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tablero 2440 × 2150</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lámina</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Misma referencia cocina</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">44 piezas RH15, más el listón de pino del bastidor (fila Pino). Encaje encontrado en 5 láminas, con sierra 4 mm y refilado 10 mm por lado. La presencia de fondos y hojas grandes aumenta consumo. Proveedor define plano final.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">despiece-cocina.xlsx, Compras; precio de referencia 27/10/2026.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Canto rígido Cartagena</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rollo 19 × 2 mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">rollo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Referencia cocina</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cantidad exclusiva de este clóset, calculada en Cantos. No se han descontado sobrantes de otros muebles. Para acabado manual: ver «Metros faltantes por comprar» al final de Pedido de corte; descontar material ya disponible. Precio por metro suelto y pegante por cotizar.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">despiece-cocina.xlsx, Compras.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Canto flexible Cartagena</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Rollo 19 × 0,45 mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HRE320-45</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Riel lateral 450 mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">par</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Precio aportado</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Vano 830 − 27 = caja 803 × 450. Los 45 kg nominales del par no certifican la caja ni la carga útil. Incluye 12 tornillos de 12 mm por par. Confirmar uniones.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Usuario; ficha HRE320/330 rev. 15/05/25.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">FSCPCM20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Kit Peralma para dos hojas</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">kit</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Candidato</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Kit publicado: 4 rodamientos, 1 guía, 1 tope y tornillos. Identificar si coinciden con la guía y el amortiguador descritos por el usuario, antes de añadir accesorios. Cada hoja RH pesa 21,3 kg sin herrajes (10,05 kg/m², dato de Madecentro); el kit indica 30 kg: preguntar si es por hoja o por kit de dos.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://madecentro.com/products/kit-de-accesorios-para-sistema-colgante; precio aportado por usuario.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">PERALMA50B · 2 m</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Riel colgante superior para 2 hojas</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">barra</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Barra 2 m para recorrido 1920 mm. Referencia real: zona de 70 mm de fondo, hojas entre 500 y 550 mm, cuerpo hasta 560. El riel se atornilla al listón de pino del bastidor (no a la tapa). Guía inferior sin apoyo de peso; no hay riel inferior de carga. Confirmar sección y taladros del sistema.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">https://madecentro.com/products/sistema-corredizo-colgate-x-3mtr</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">HMA310-02</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Manija tubular CC96 mm</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">unidad</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Elegida</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Una manija vertical en el extremo exterior de cada hoja.35 mm de saliente: fondo máximo 585 mm. Dos centros 96 mm; largo representado 119 mm. Las manijas no sustituyen una certificación de rigidez del tablero.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Usuario: $2.743/unidad. https://madecentro.com/products/hma310-02-manija-310-acero-inox-cc-96-mm-rectangular-alta</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Verificar con FSCPCM20</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tope plástico amortiguado</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">conjunto</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Verificar incluido</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Detrás de la hoja exterior, conserva 50 mm de desfase y evita invertir el orden de hojas. Cota de pérdida de recorrido aportada por el usuario. Verificar si viene en el kit; no duplicar compra. La guía inferior tampoco se compra dos veces.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Descripción y fotos del clóset real del usuario; referencia comercial pendiente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Por elegir</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Barras para colgar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">tramo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Cotizar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Una ilustrada 810 mm y dos 1055 mm. Barra baja derecha desmontable. Medidas de corte reales según soportes elegidos.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Modelo; no representa una referencia comercial confirmada.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Soportes de barra</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dos por barra. Fijación y carga para RH15 por confirmar.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Montaje pendiente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Por dimensionar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Apoyos de base</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Dos bajo cada lateral/divisor. El modelo dibuja 20 mm de apoyo y base total 100 mm; producto y regulación por elegir.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Geometría propuesta.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Uniones y anclajes</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">lote</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye fijación de fondos, estructura y refuerzos de RH; el bastidor del riel se lista aparte. El extremo derecho queda libre: no puede anclarse al muro lateral derecho. Definir anclaje posterior y lateral izquierdo según muro.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Montaje y sustrato real.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Pino · por cotizar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Listón 4×4 cm · bastidor del riel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">listón</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Listón de pino de 4×4 cm que va de lateral a lateral: 1920 mm libres más el encaje en cada lateral (máx. 7 mm por lado). Pedir de 2,0 m o más, recto, seco y sin nudos grandes; sobra para 2 tacos de 15 mm. Va encajonado y atornillado a los laterales; el riel (50 mm) se atornilla a su cara inferior y sobresale ~5 mm por lado. El clóset real usa 7×3 cm; se cambió a 4×4 por disponibilidad. Confirmar rebaje y tornillos con el instalador.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Descripción del clóset real del usuario, 27/10/2026; precio pendiente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tornillos del bastidor y del riel</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tornillos para madera y aglomerado en cada extremo del listón y para el riel; el kit del sistema puede traer los suyos. Escuadras solo si el rebaje en los laterales queda corto.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Por cotizar</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Corte, canteado e instalación</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">servicio</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Confirmar plantilla de las hojas y perfiles, guías y topes adicionales, veta y suministro. Mantener todo este presupuesto independiente.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Proveedor.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">SUBTOTAL PARCIAL</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Incluye 2 manijas por $5.486. Quedan listón de pino, tornillos, barras, apoyos, uniones, anclajes y servicios. Verificar accesorios incluidos. No hay PERALM93 presupuestado en este diseño.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Clóset compacto: cantos exclusivos</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Reserva/borde m</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Tipo</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Aplicación</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Bordes</x:t>
   </x:si>
   <x:si>
@@ -711,9 +627,6 @@
     <x:t xml:space="preserve">Proveedor de corte</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Confirmar Q2–Q4 del Pedido de corte (medida terminada y tamaño mínimo que cantea). Encaje previsto en 5 láminas.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Pedido de corte</x:t>
   </x:si>
   <x:si>
@@ -759,9 +672,6 @@
     <x:t xml:space="preserve">Anclajes</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Anclaje al muro posterior e izquierdo; el extremo derecho queda libre. Definir tornillería y uniones de los fondos.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Instalación</x:t>
   </x:si>
   <x:si>
@@ -828,9 +738,6 @@
     <x:t xml:space="preserve">Fondo interior</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">Zona de referencia 490–560 mm. Hoja interior 500–515; exterior 535–550. Cuerpo 560 y manijas hasta 585. Fondo RH15 de 0–15 deja 485 mm útiles. Los 7 cm son la zona de referencia del marco, no un espesor adicional del cuerpo.</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Medidas y aclaraciones del usuario / modelo.</x:t>
   </x:si>
   <x:si>
@@ -862,9 +769,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Material y alcance</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Misma referencia RH15 Cartagena que la cocina final. Despiece y compras exclusivos del clóset compacto; no se han fusionado con cocina ni baño.</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">Solicitud del usuario y Excel de cocina.</x:t>
@@ -1021,7 +925,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="56">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -1116,6 +1020,27 @@
     </x:xf>
     <x:xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="2" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="2" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="1" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <x:xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <x:xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <x:xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1436,8 +1361,8 @@
       <x:c r="P3" s="1"/>
     </x:row>
     <x:row r="4" ht="15" customHeight="1">
-      <x:c r="A4" s="1" t="s">
-        <x:v>2</x:v>
+      <x:c r="A4" s="1" t="str">
+        <x:v>Medidas terminadas; veta en E. Sin paneles C3-005/C3-011: marco posterior completo C3-025 a C3-030 de 100 mm de ancho, RH15. Flexible solo en el borde largo libre hacia el cuadro interior; uniones ocultas sin canto. Anclajes por dimensionar.</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -1475,63 +1400,63 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="3" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B6" s="3" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="B6" s="3" t="s">
+      <x:c r="C6" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C6" s="3" t="s">
+      <x:c r="D6" s="3" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="D6" s="3" t="s">
+      <x:c r="E6" s="3" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E6" s="3" t="s">
+      <x:c r="F6" s="3" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="F6" s="3" t="s">
+      <x:c r="G6" s="3" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="G6" s="3" t="s">
+      <x:c r="H6" s="3" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="H6" s="3" t="s">
+      <x:c r="I6" s="3" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="I6" s="3" t="s">
+      <x:c r="J6" s="3" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="J6" s="3" t="s">
+      <x:c r="K6" s="3" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="K6" s="3" t="s">
+      <x:c r="L6" s="3" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="L6" s="3" t="s">
+      <x:c r="M6" s="3" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="M6" s="3" t="s">
+      <x:c r="N6" s="3" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="N6" s="3" t="s">
+      <x:c r="O6" s="3" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="O6" s="3" t="s">
+      <x:c r="P6" s="3" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="P6" s="3" t="s">
-        <x:v>18</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B7" s="1" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B7" s="1" t="s">
+      <x:c r="C7" s="4" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="C7" s="4" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="D7" s="1">
         <x:v>2</x:v>
@@ -1570,21 +1495,21 @@
         <x:v>559.55</x:v>
       </x:c>
       <x:c r="O7" s="7" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="P7" s="4" t="s">
         <x:v>22</x:v>
-      </x:c>
-      <x:c r="P7" s="4" t="s">
-        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B8" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="B8" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="D8" s="1">
         <x:v>1</x:v>
@@ -1623,21 +1548,21 @@
         <x:v>489.55</x:v>
       </x:c>
       <x:c r="O8" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P8" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="1" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
         <x:v>27</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="C9" s="4" t="s">
         <x:v>28</x:v>
-      </x:c>
-      <x:c r="C9" s="4" t="s">
-        <x:v>29</x:v>
       </x:c>
       <x:c r="D9" s="1">
         <x:v>1</x:v>
@@ -1676,21 +1601,21 @@
         <x:v>559.55</x:v>
       </x:c>
       <x:c r="O9" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P9" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="s">
         <x:v>31</x:v>
-      </x:c>
-      <x:c r="B10" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C10" s="4" t="s">
-        <x:v>32</x:v>
       </x:c>
       <x:c r="D10" s="1">
         <x:v>1</x:v>
@@ -1729,74 +1654,74 @@
         <x:v>504.55</x:v>
       </x:c>
       <x:c r="O10" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P10" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="B11" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D11" s="1">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="110" customHeight="1">
+      <x:c r="A11" s="1" t="str">
+        <x:v>C3-025</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="str">
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="C11" s="43" t="str">
+        <x:v>Amarre posterior superior izquierdo</x:v>
+      </x:c>
+      <x:c r="D11" s="43" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E11" s="1">
-        <x:v>2250</x:v>
-      </x:c>
-      <x:c r="F11" s="1">
+      <x:c r="E11" s="43" t="n">
         <x:v>830</x:v>
       </x:c>
-      <x:c r="G11" s="1">
+      <x:c r="F11" s="43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G11" s="43" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H11" s="5" t="n">
+      <x:c r="H11" s="51" t="n">
         <x:f t="shared" si="0">D11*E11*F11/1000000</x:f>
-        <x:v>1.8675</x:v>
-      </x:c>
-      <x:c r="I11" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="J11" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="K11" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="L11" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="M11" s="6" t="n">
+        <x:v>0.083</x:v>
+      </x:c>
+      <x:c r="I11" s="42" t="str">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="J11" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K11" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L11" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M11" s="52" t="n">
         <x:f t="shared" si="1">E11-IF(K11="2",2,IF(K11="0.45",0.45,0))-IF(L11="2",2,IF(L11="0.45",0.45,0))</x:f>
-        <x:v>2250</x:v>
-      </x:c>
-      <x:c r="N11" s="6" t="n">
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="N11" s="52" t="n">
         <x:f t="shared" si="2">F11-IF(I11="2",2,IF(I11="0.45",0.45,0))-IF(J11="2",2,IF(J11="0.45",0.45,0))</x:f>
-        <x:v>830</x:v>
-      </x:c>
-      <x:c r="O11" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P11" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>99.55</x:v>
+      </x:c>
+      <x:c r="O11" s="53" t="str">
+        <x:v>Diseño elegido; anclajes por dimensionar</x:v>
+      </x:c>
+      <x:c r="P11" s="43" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C12" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D12" s="1">
         <x:v>1</x:v>
@@ -1835,21 +1760,21 @@
         <x:v>474.55</x:v>
       </x:c>
       <x:c r="O12" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P12" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C13" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D13" s="1">
         <x:v>1</x:v>
@@ -1888,21 +1813,21 @@
         <x:v>79.55</x:v>
       </x:c>
       <x:c r="O13" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P13" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C14" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D14" s="1">
         <x:v>1</x:v>
@@ -1941,21 +1866,21 @@
         <x:v>99.55</x:v>
       </x:c>
       <x:c r="O14" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P14" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D15" s="1">
         <x:v>1</x:v>
@@ -1994,21 +1919,21 @@
         <x:v>559.55</x:v>
       </x:c>
       <x:c r="O15" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P15" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D16" s="1">
         <x:v>1</x:v>
@@ -2047,74 +1972,74 @@
         <x:v>504.55</x:v>
       </x:c>
       <x:c r="O16" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P16" s="4" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" ht="54" customHeight="1">
-      <x:c r="A17" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C17" s="4" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="D17" s="1">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="110" customHeight="1">
+      <x:c r="A17" s="1" t="str">
+        <x:v>C3-026</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="str">
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="C17" s="43" t="str">
+        <x:v>Amarre posterior superior derecho</x:v>
+      </x:c>
+      <x:c r="D17" s="43" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E17" s="1">
-        <x:v>2250</x:v>
-      </x:c>
-      <x:c r="F17" s="1">
+      <x:c r="E17" s="43" t="n">
         <x:v>1075</x:v>
       </x:c>
-      <x:c r="G17" s="1">
+      <x:c r="F17" s="43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G17" s="43" t="n">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="H17" s="5" t="n">
+      <x:c r="H17" s="51" t="n">
         <x:f t="shared" si="0">D17*E17*F17/1000000</x:f>
-        <x:v>2.41875</x:v>
-      </x:c>
-      <x:c r="I17" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="J17" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="K17" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="L17" s="12" t="str">
-        <x:v>—</x:v>
-      </x:c>
-      <x:c r="M17" s="6" t="n">
+        <x:v>0.1075</x:v>
+      </x:c>
+      <x:c r="I17" s="42" t="str">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="J17" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K17" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L17" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M17" s="52" t="n">
         <x:f t="shared" si="1">E17-IF(K17="2",2,IF(K17="0.45",0.45,0))-IF(L17="2",2,IF(L17="0.45",0.45,0))</x:f>
-        <x:v>2250</x:v>
-      </x:c>
-      <x:c r="N17" s="6" t="n">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="N17" s="52" t="n">
         <x:f t="shared" si="2">F17-IF(I17="2",2,IF(I17="0.45",0.45,0))-IF(J17="2",2,IF(J17="0.45",0.45,0))</x:f>
-        <x:v>1075</x:v>
-      </x:c>
-      <x:c r="O17" s="7" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="P17" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>99.55</x:v>
+      </x:c>
+      <x:c r="O17" s="53" t="str">
+        <x:v>Diseño elegido; anclajes por dimensionar</x:v>
+      </x:c>
+      <x:c r="P17" s="43" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C18" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>1</x:v>
@@ -2153,21 +2078,21 @@
         <x:v>474.55</x:v>
       </x:c>
       <x:c r="O18" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P18" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C19" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D19" s="1">
         <x:v>1</x:v>
@@ -2206,21 +2131,21 @@
         <x:v>79.55</x:v>
       </x:c>
       <x:c r="O19" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P19" s="4" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C20" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D20" s="1">
         <x:v>1</x:v>
@@ -2259,21 +2184,21 @@
         <x:v>99.55</x:v>
       </x:c>
       <x:c r="O20" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P20" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C21" s="4" t="s">
-        <x:v>54</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D21" s="1">
         <x:v>3</x:v>
@@ -2312,21 +2237,21 @@
         <x:v>206</x:v>
       </x:c>
       <x:c r="O21" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P21" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C22" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D22" s="1">
         <x:v>6</x:v>
@@ -2365,21 +2290,21 @@
         <x:v>154.55</x:v>
       </x:c>
       <x:c r="O22" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P22" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C23" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D23" s="1">
         <x:v>3</x:v>
@@ -2418,21 +2343,21 @@
         <x:v>449.55</x:v>
       </x:c>
       <x:c r="O23" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P23" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C24" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D24" s="1">
         <x:v>6</x:v>
@@ -2471,21 +2396,21 @@
         <x:v>154.55</x:v>
       </x:c>
       <x:c r="O24" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P24" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C25" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D25" s="1">
         <x:v>3</x:v>
@@ -2524,21 +2449,21 @@
         <x:v>39.55</x:v>
       </x:c>
       <x:c r="O25" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P25" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C26" s="4" t="s">
-        <x:v>68</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="1">
         <x:v>1</x:v>
@@ -2577,21 +2502,21 @@
         <x:v>91.1</x:v>
       </x:c>
       <x:c r="O26" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P26" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C27" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D27" s="1">
         <x:v>1</x:v>
@@ -2630,21 +2555,21 @@
         <x:v>79.1</x:v>
       </x:c>
       <x:c r="O27" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P27" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="54" customHeight="1">
       <x:c r="A28" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="C28" s="4" t="s">
         <x:v>67</x:v>
-      </x:c>
-      <x:c r="C28" s="4" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="D28" s="1">
         <x:v>3</x:v>
@@ -2683,21 +2608,21 @@
         <x:v>79.1</x:v>
       </x:c>
       <x:c r="O28" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P28" s="4" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="54" customHeight="1">
       <x:c r="A29" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C29" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D29" s="1">
         <x:v>2</x:v>
@@ -2736,21 +2661,21 @@
         <x:v>971</x:v>
       </x:c>
       <x:c r="O29" s="7" t="s">
-        <x:v>76</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="P29" s="13" t="s">
-        <x:v>77</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C30" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D30" s="1">
         <x:v>1</x:v>
@@ -2789,95 +2714,271 @@
         <x:v>119.1</x:v>
       </x:c>
       <x:c r="O30" s="7" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="P30" s="4" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" ht="15" customHeight="1">
-      <x:c r="A31" s="1"/>
-      <x:c r="B31" s="1"/>
-      <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
-      <x:c r="F31" s="1"/>
-      <x:c r="G31" s="1"/>
-      <x:c r="H31" s="5"/>
-      <x:c r="I31" s="1"/>
-      <x:c r="J31" s="1"/>
-      <x:c r="K31" s="1"/>
-      <x:c r="L31" s="1"/>
-      <x:c r="M31" s="1"/>
-      <x:c r="N31" s="1"/>
-      <x:c r="O31" s="1"/>
-      <x:c r="P31" s="1"/>
-    </x:row>
-    <x:row r="32" ht="15" customHeight="1">
-      <x:c r="A32" s="1"/>
-      <x:c r="B32" s="1"/>
-      <x:c r="C32" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D32" s="1" t="n">
-        <x:f>SUM(D7:D30)</x:f>
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="E32" s="1"/>
-      <x:c r="F32" s="1"/>
-      <x:c r="G32" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="H32" s="5" t="n">
-        <x:f>SUM(H7:H30)</x:f>
-        <x:v>18.99642</x:v>
-      </x:c>
-      <x:c r="I32" s="1"/>
-      <x:c r="J32" s="1"/>
-      <x:c r="K32" s="1"/>
-      <x:c r="L32" s="1"/>
-      <x:c r="M32" s="1"/>
-      <x:c r="N32" s="1"/>
-      <x:c r="O32" s="1"/>
-      <x:c r="P32" s="1"/>
-    </x:row>
-    <x:row r="33" ht="15" customHeight="1">
-      <x:c r="A33" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="B33" s="1"/>
-      <x:c r="C33" s="1"/>
-      <x:c r="D33" s="1"/>
-      <x:c r="E33" s="1"/>
-      <x:c r="F33" s="1"/>
-      <x:c r="G33" s="1"/>
-      <x:c r="H33" s="1"/>
-      <x:c r="I33" s="1"/>
-      <x:c r="J33" s="1"/>
-      <x:c r="K33" s="1"/>
-      <x:c r="L33" s="1"/>
-      <x:c r="M33" s="1"/>
-      <x:c r="N33" s="1"/>
-      <x:c r="O33" s="1"/>
-      <x:c r="P33" s="1"/>
-    </x:row>
-    <x:row r="34" ht="15" customHeight="1">
-      <x:c r="A34" s="1"/>
-      <x:c r="B34" s="1"/>
-      <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
-      <x:c r="F34" s="1"/>
-      <x:c r="G34" s="1"/>
-      <x:c r="H34" s="1"/>
-      <x:c r="I34" s="1"/>
-      <x:c r="J34" s="1"/>
-      <x:c r="K34" s="1"/>
-      <x:c r="L34" s="1"/>
-      <x:c r="M34" s="1"/>
-      <x:c r="N34" s="1"/>
-      <x:c r="O34" s="1"/>
-      <x:c r="P34" s="1"/>
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="110" customHeight="1">
+      <x:c r="A31" s="1" t="str">
+        <x:v>C3-027</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="str">
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="C31" s="43" t="str">
+        <x:v>Montante posterior derecho</x:v>
+      </x:c>
+      <x:c r="D31" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E31" s="43" t="n">
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="F31" s="43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G31" s="43" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H31" s="51" t="n">
+        <x:f>D31*E31*F31/1000000</x:f>
+        <x:v>0.205</x:v>
+      </x:c>
+      <x:c r="I31" s="42" t="str">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="J31" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K31" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L31" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M31" s="52" t="n">
+        <x:f>E31-IF(K31="2",2,IF(K31="0.45",0.45,0))-IF(L31="2",2,IF(L31="0.45",0.45,0))</x:f>
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="N31" s="52" t="n">
+        <x:f>F31-IF(I31="2",2,IF(I31="0.45",0.45,0))-IF(J31="2",2,IF(J31="0.45",0.45,0))</x:f>
+        <x:v>99.55</x:v>
+      </x:c>
+      <x:c r="O31" s="53" t="str">
+        <x:v>Diseño elegido; anclajes por dimensionar</x:v>
+      </x:c>
+      <x:c r="P31" s="43" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="110" customHeight="1">
+      <x:c r="A32" s="1" t="str">
+        <x:v>C3-028</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="str">
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="C32" s="43" t="str">
+        <x:v>Montante posterior izquierdo</x:v>
+      </x:c>
+      <x:c r="D32" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E32" s="43" t="n">
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="F32" s="43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G32" s="43" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H32" s="51" t="n">
+        <x:f>D32*E32*F32/1000000</x:f>
+        <x:v>0.205</x:v>
+      </x:c>
+      <x:c r="I32" s="42" t="str">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="J32" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K32" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L32" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M32" s="52" t="n">
+        <x:f>E32-IF(K32="2",2,IF(K32="0.45",0.45,0))-IF(L32="2",2,IF(L32="0.45",0.45,0))</x:f>
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="N32" s="52" t="n">
+        <x:f>F32-IF(I32="2",2,IF(I32="0.45",0.45,0))-IF(J32="2",2,IF(J32="0.45",0.45,0))</x:f>
+        <x:v>99.55</x:v>
+      </x:c>
+      <x:c r="O32" s="53" t="str">
+        <x:v>Diseño elegido; anclajes por dimensionar</x:v>
+      </x:c>
+      <x:c r="P32" s="43" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="110" customHeight="1">
+      <x:c r="A33" s="1" t="str">
+        <x:v>C3-029</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="str">
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="C33" s="43" t="str">
+        <x:v>Amarre posterior inferior izquierdo</x:v>
+      </x:c>
+      <x:c r="D33" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E33" s="43" t="n">
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="F33" s="43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G33" s="43" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H33" s="51" t="n">
+        <x:f>D33*E33*F33/1000000</x:f>
+        <x:v>0.083</x:v>
+      </x:c>
+      <x:c r="I33" s="42" t="str">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="J33" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K33" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L33" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M33" s="52" t="n">
+        <x:f>E33-IF(K33="2",2,IF(K33="0.45",0.45,0))-IF(L33="2",2,IF(L33="0.45",0.45,0))</x:f>
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="N33" s="52" t="n">
+        <x:f>F33-IF(I33="2",2,IF(I33="0.45",0.45,0))-IF(J33="2",2,IF(J33="0.45",0.45,0))</x:f>
+        <x:v>99.55</x:v>
+      </x:c>
+      <x:c r="O33" s="53" t="str">
+        <x:v>Diseño elegido; anclajes por dimensionar</x:v>
+      </x:c>
+      <x:c r="P33" s="43" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="110" customHeight="1">
+      <x:c r="A34" s="1" t="str">
+        <x:v>C3-030</x:v>
+      </x:c>
+      <x:c r="B34" s="1" t="str">
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="C34" s="43" t="str">
+        <x:v>Amarre posterior inferior derecho</x:v>
+      </x:c>
+      <x:c r="D34" s="43" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E34" s="43" t="n">
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="F34" s="43" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="G34" s="43" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H34" s="51" t="n">
+        <x:f>D34*E34*F34/1000000</x:f>
+        <x:v>0.1075</x:v>
+      </x:c>
+      <x:c r="I34" s="42" t="str">
+        <x:v>0.45</x:v>
+      </x:c>
+      <x:c r="J34" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K34" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L34" s="42" t="str">
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="M34" s="52" t="n">
+        <x:f>E34-IF(K34="2",2,IF(K34="0.45",0.45,0))-IF(L34="2",2,IF(L34="0.45",0.45,0))</x:f>
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="N34" s="52" t="n">
+        <x:f>F34-IF(I34="2",2,IF(I34="0.45",0.45,0))-IF(J34="2",2,IF(J34="0.45",0.45,0))</x:f>
+        <x:v>99.55</x:v>
+      </x:c>
+      <x:c r="O34" s="53" t="str">
+        <x:v>Diseño elegido; anclajes por dimensionar</x:v>
+      </x:c>
+      <x:c r="P34" s="43" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1" t="str">
+        <x:v>TOTAL RH15</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="n">
+        <x:f>SUM(D7:D34)</x:f>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1" t="str">
+        <x:v>Área neta</x:v>
+      </x:c>
+      <x:c r="H36" s="5" t="n">
+        <x:f>SUM(H7:H34)</x:f>
+        <x:v>15.50117</x:v>
+      </x:c>
+      <x:c r="I36" s="1"/>
+      <x:c r="J36" s="1"/>
+      <x:c r="K36" s="1"/>
+      <x:c r="L36" s="1"/>
+      <x:c r="M36" s="1"/>
+      <x:c r="N36" s="1"/>
+      <x:c r="O36" s="1"/>
+      <x:c r="P36" s="1"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="1" t="str">
+        <x:v>Listón de pino del bastidor del riel fuera del total: ver Compras.</x:v>
+      </x:c>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="1"/>
+      <x:c r="D37" s="1"/>
+      <x:c r="E37" s="1"/>
+      <x:c r="F37" s="1"/>
+      <x:c r="G37" s="1"/>
+      <x:c r="H37" s="1"/>
+      <x:c r="I37" s="1"/>
+      <x:c r="J37" s="1"/>
+      <x:c r="K37" s="1"/>
+      <x:c r="L37" s="1"/>
+      <x:c r="M37" s="1"/>
+      <x:c r="N37" s="1"/>
+      <x:c r="O37" s="1"/>
+      <x:c r="P37" s="1"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2906,24 +3007,24 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="S1" s="14" t="s">
-        <x:v>84</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="17.399999618530273">
       <x:c r="A2" s="15" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="P2" s="17" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q2" s="18" t="s">
-        <x:v>87</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S2" s="14" t="s">
-        <x:v>19</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="T2" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2931,82 +3032,94 @@
         <x:v>Medidas finales con canto incluido. R = rígido 2 mm; F = flexible 0,45 mm; — = sin canto. Un solo tipo por pieza; solo se cantean los bordes marcados.</x:v>
       </x:c>
       <x:c r="P3" s="17" t="s">
-        <x:v>89</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q3" s="26">
         <x:v>100</x:v>
       </x:c>
       <x:c r="S3" s="14" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="T3" s="14" t="s">
-        <x:v>90</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="14" t="s">
-        <x:v>91</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="P4" s="17" t="s">
-        <x:v>92</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q4" s="26">
         <x:v>250</x:v>
       </x:c>
       <x:c r="S4" s="14" t="s">
-        <x:v>73</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="T4" s="14" t="s">
-        <x:v>93</x:v>
+        <x:v>85</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="P5" s="17" t="s">
-        <x:v>94</x:v>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="S5" t="str">
+        <x:v>C3-025</x:v>
+      </x:c>
+      <x:c r="T5" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="26.399999618530273">
       <x:c r="A6" s="19" t="s">
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B6" s="19" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C6" s="19" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="D6" s="19" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E6" s="19" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F6" s="19" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G6" s="19" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H6" s="19" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="I6" s="19" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="J6" s="19" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="K6" s="19" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="L6" s="19" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C6" s="19" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="19" t="s">
+      <x:c r="M6" s="19" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="E6" s="19" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="F6" s="19" t="s">
+      <x:c r="N6" s="19" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="G6" s="19" t="s">
-        <x:v>98</x:v>
-      </x:c>
-      <x:c r="H6" s="19" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="I6" s="19" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="J6" s="19" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="K6" s="19" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="L6" s="19" t="s">
-        <x:v>103</x:v>
-      </x:c>
-      <x:c r="M6" s="19" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="N6" s="19" t="s">
-        <x:v>105</x:v>
+      <x:c r="S6" t="str">
+        <x:v>C3-026</x:v>
+      </x:c>
+      <x:c r="T6" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -3066,6 +3179,12 @@
         <x:f>IF(LEN(TRIM(IF($L7="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M7,2)&amp;" × "&amp;ROUND(Despiece!N7,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A7,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L7="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M7,2)&amp;" × "&amp;ROUND(Despiece!N7,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A7,$S$2:$T$40,2,FALSE),"")))</x:f>
         <x:v>Rebaje superior para el listón de pino 4 × 4 en taller.</x:v>
       </x:c>
+      <x:c r="S7" t="str">
+        <x:v>C3-027</x:v>
+      </x:c>
+      <x:c r="T7" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="20" t="str">
@@ -3124,6 +3243,12 @@
         <x:f>IF(LEN(TRIM(IF($L8="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M8,2)&amp;" × "&amp;ROUND(Despiece!N8,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A8,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L8="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M8,2)&amp;" × "&amp;ROUND(Despiece!N8,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A8,$S$2:$T$40,2,FALSE),"")))</x:f>
         <x:v>—</x:v>
       </x:c>
+      <x:c r="S8" t="str">
+        <x:v>C3-028</x:v>
+      </x:c>
+      <x:c r="T8" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="20" t="str">
@@ -3182,6 +3307,12 @@
         <x:f>IF(LEN(TRIM(IF($L9="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M9,2)&amp;" × "&amp;ROUND(Despiece!N9,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A9,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L9="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M9,2)&amp;" × "&amp;ROUND(Despiece!N9,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A9,$S$2:$T$40,2,FALSE),"")))</x:f>
         <x:v>—</x:v>
       </x:c>
+      <x:c r="S9" t="str">
+        <x:v>C3-029</x:v>
+      </x:c>
+      <x:c r="T9" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="20" t="str">
@@ -3240,11 +3371,17 @@
         <x:f>IF(LEN(TRIM(IF($L10="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M10,2)&amp;" × "&amp;ROUND(Despiece!N10,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A10,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L10="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M10,2)&amp;" × "&amp;ROUND(Despiece!N10,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A10,$S$2:$T$40,2,FALSE),"")))</x:f>
         <x:v>—</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11">
+      <x:c r="S10" t="str">
+        <x:v>C3-030</x:v>
+      </x:c>
+      <x:c r="T10" t="str">
+        <x:v>Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="110" customHeight="1">
       <x:c r="A11" s="20" t="str">
         <x:f>Despiece!A11</x:f>
-        <x:v>C3-005</x:v>
+        <x:v>C3-025</x:v>
       </x:c>
       <x:c r="B11" s="20" t="str">
         <x:f>Despiece!B11</x:f>
@@ -3252,7 +3389,7 @@
       </x:c>
       <x:c r="C11" s="20" t="str">
         <x:f>Despiece!C11</x:f>
-        <x:v>Fondo RH15</x:v>
+        <x:v>Amarre posterior superior izquierdo</x:v>
       </x:c>
       <x:c r="D11" s="20" t="str">
         <x:f>"RH15 Cartagena "&amp;Despiece!G11&amp;" mm"</x:f>
@@ -3264,15 +3401,15 @@
       </x:c>
       <x:c r="F11" s="31" t="n">
         <x:f>IF($Q$2="NO",ROUND(Despiece!M11,2),Despiece!E11)</x:f>
-        <x:v>2250</x:v>
+        <x:v>830</x:v>
       </x:c>
       <x:c r="G11" s="31" t="n">
         <x:f>IF($Q$2="NO",ROUND(Despiece!N11,2),Despiece!F11)</x:f>
-        <x:v>830</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H11" s="21" t="str">
         <x:f>IF(Despiece!I11="2","R",IF(Despiece!I11="0.45","F","—"))</x:f>
-        <x:v>—</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="I11" s="21" t="str">
         <x:f>IF(Despiece!J11="2","R",IF(Despiece!J11="0.45","F","—"))</x:f>
@@ -3288,15 +3425,15 @@
       </x:c>
       <x:c r="L11" s="21" t="str">
         <x:f>IF(SUMPRODUCT((Despiece!I11:L11="2")+(Despiece!I11:L11="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M11,Despiece!N11)&lt;$Q$3,MAX(Despiece!M11,Despiece!N11)&lt;$Q$4),"Pequeña","Normal"))</x:f>
-        <x:v>Sin canto</x:v>
+        <x:v>Pequeña</x:v>
       </x:c>
       <x:c r="M11" s="20" t="str">
         <x:f>Despiece!E11&amp;" × "&amp;Despiece!F11</x:f>
-        <x:v>2250 × 830</x:v>
-      </x:c>
-      <x:c r="N11" s="22" t="str">
+        <x:v>830 × 100</x:v>
+      </x:c>
+      <x:c r="N11" s="54" t="str">
         <x:f>IF(LEN(TRIM(IF($L11="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M11,2)&amp;" × "&amp;ROUND(Despiece!N11,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A11,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L11="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M11,2)&amp;" × "&amp;ROUND(Despiece!N11,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A11,$S$2:$T$40,2,FALSE),"")))</x:f>
-        <x:v>—</x:v>
+        <x:v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -3589,10 +3726,10 @@
         <x:v>—</x:v>
       </x:c>
     </x:row>
-    <x:row r="17">
+    <x:row r="17" ht="110" customHeight="1">
       <x:c r="A17" s="20" t="str">
         <x:f>Despiece!A17</x:f>
-        <x:v>C3-011</x:v>
+        <x:v>C3-026</x:v>
       </x:c>
       <x:c r="B17" s="20" t="str">
         <x:f>Despiece!B17</x:f>
@@ -3600,7 +3737,7 @@
       </x:c>
       <x:c r="C17" s="20" t="str">
         <x:f>Despiece!C17</x:f>
-        <x:v>Fondo RH15</x:v>
+        <x:v>Amarre posterior superior derecho</x:v>
       </x:c>
       <x:c r="D17" s="20" t="str">
         <x:f>"RH15 Cartagena "&amp;Despiece!G17&amp;" mm"</x:f>
@@ -3612,15 +3749,15 @@
       </x:c>
       <x:c r="F17" s="31" t="n">
         <x:f>IF($Q$2="NO",ROUND(Despiece!M17,2),Despiece!E17)</x:f>
-        <x:v>2250</x:v>
+        <x:v>1075</x:v>
       </x:c>
       <x:c r="G17" s="31" t="n">
         <x:f>IF($Q$2="NO",ROUND(Despiece!N17,2),Despiece!F17)</x:f>
-        <x:v>1075</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H17" s="21" t="str">
         <x:f>IF(Despiece!I17="2","R",IF(Despiece!I17="0.45","F","—"))</x:f>
-        <x:v>—</x:v>
+        <x:v>F</x:v>
       </x:c>
       <x:c r="I17" s="21" t="str">
         <x:f>IF(Despiece!J17="2","R",IF(Despiece!J17="0.45","F","—"))</x:f>
@@ -3636,15 +3773,15 @@
       </x:c>
       <x:c r="L17" s="21" t="str">
         <x:f>IF(SUMPRODUCT((Despiece!I17:L17="2")+(Despiece!I17:L17="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M17,Despiece!N17)&lt;$Q$3,MAX(Despiece!M17,Despiece!N17)&lt;$Q$4),"Pequeña","Normal"))</x:f>
-        <x:v>Sin canto</x:v>
+        <x:v>Pequeña</x:v>
       </x:c>
       <x:c r="M17" s="20" t="str">
         <x:f>Despiece!E17&amp;" × "&amp;Despiece!F17</x:f>
-        <x:v>2250 × 1075</x:v>
-      </x:c>
-      <x:c r="N17" s="22" t="str">
+        <x:v>1075 × 100</x:v>
+      </x:c>
+      <x:c r="N17" s="54" t="str">
         <x:f>IF(LEN(TRIM(IF($L17="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M17,2)&amp;" × "&amp;ROUND(Despiece!N17,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A17,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L17="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M17,2)&amp;" × "&amp;ROUND(Despiece!N17,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A17,$S$2:$T$40,2,FALSE),"")))</x:f>
-        <x:v>—</x:v>
+        <x:v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo inferior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -4389,7 +4526,7 @@
         <x:v>F</x:v>
       </x:c>
       <x:c r="L30" s="21" t="str">
-        <x:f>IF(SUMPRODUCT((Despiece!I30:L30="2")+(Despiece!I30:L30="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M30,Despiece!N30)&lt;$Q$3,MAX(Despiece!M30,Despiece!N30)&lt;$Q$4),"Pequeña","Normal"))</x:f>
+        <x:f>IF(SUMPRODUCT((Despiece!I30:L34="2")+(Despiece!I30:L34="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M30,Despiece!N30)&lt;$Q$3,MAX(Despiece!M30,Despiece!N30)&lt;$Q$4),"Pequeña","Normal"))</x:f>
         <x:v>Normal</x:v>
       </x:c>
       <x:c r="M30" s="20" t="str">
@@ -4401,209 +4538,606 @@
         <x:v>—</x:v>
       </x:c>
     </x:row>
-    <x:row r="32">
-      <x:c r="C32" s="16" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="D32" s="23"/>
-      <x:c r="E32" s="23"/>
-      <x:c r="F32" s="16" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="G32" s="16" t="s">
-        <x:v>108</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33">
-      <x:c r="C33" s="16" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D33" s="23"/>
-      <x:c r="E33" s="23"/>
-      <x:c r="F33" s="24" t="n">
-        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="2")+(Despiece!$J$7:$J$30="2"),--($L$7:$L$30="Normal"))+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="2")+(Despiece!$L$7:$L$30="2"),--($L$7:$L$30="Normal")))/1000</x:f>
-        <x:v>18.804</x:v>
-      </x:c>
-      <x:c r="G33" s="24" t="n">
-        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="2")+(Despiece!$J$7:$J$30="2"),--($L$7:$L$30="Pequeña"))+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="2")+(Despiece!$L$7:$L$30="2"),--($L$7:$L$30="Pequeña")))/1000</x:f>
-        <x:v>0</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34">
-      <x:c r="C34" s="16" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="D34" s="23"/>
-      <x:c r="E34" s="23"/>
-      <x:c r="F34" s="24" t="n">
-        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="0.45")+(Despiece!$J$7:$J$30="0.45"),--($L$7:$L$30="Normal"))+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="0.45")+(Despiece!$L$7:$L$30="0.45"),--($L$7:$L$30="Normal")))/1000</x:f>
-        <x:v>33.922</x:v>
-      </x:c>
-      <x:c r="G34" s="24" t="n">
-        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="0.45")+(Despiece!$J$7:$J$30="0.45"),--($L$7:$L$30="Pequeña"))+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="0.45")+(Despiece!$L$7:$L$30="0.45"),--($L$7:$L$30="Pequeña")))/1000</x:f>
-        <x:v>17.963</x:v>
+    <x:row r="31" ht="110" customHeight="1">
+      <x:c r="A31" s="20" t="str">
+        <x:f>Despiece!A31</x:f>
+        <x:v>C3-027</x:v>
+      </x:c>
+      <x:c r="B31" s="20" t="str">
+        <x:f>Despiece!B31</x:f>
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="C31" s="20" t="str">
+        <x:f>Despiece!C31</x:f>
+        <x:v>Montante posterior derecho</x:v>
+      </x:c>
+      <x:c r="D31" s="20" t="str">
+        <x:f>"RH15 Cartagena "&amp;Despiece!G31&amp;" mm"</x:f>
+        <x:v>RH15 Cartagena 15 mm</x:v>
+      </x:c>
+      <x:c r="E31" s="20" t="n">
+        <x:f>Despiece!D31</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F31" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!M31,2),Despiece!E31)</x:f>
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="G31" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!N31,2),Despiece!F31)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H31" s="21" t="str">
+        <x:f>IF(Despiece!I31="2","R",IF(Despiece!I31="0.45","F","—"))</x:f>
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I31" s="21" t="str">
+        <x:f>IF(Despiece!J31="2","R",IF(Despiece!J31="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J31" s="21" t="str">
+        <x:f>IF(Despiece!K31="2","R",IF(Despiece!K31="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K31" s="21" t="str">
+        <x:f>IF(Despiece!L31="2","R",IF(Despiece!L31="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L31" s="21" t="str">
+        <x:f>IF(SUMPRODUCT((Despiece!I31:L31="2")+(Despiece!I31:L31="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M31,Despiece!N31)&lt;$Q$3,MAX(Despiece!M31,Despiece!N31)&lt;$Q$4),"Pequeña","Normal"))</x:f>
+        <x:v>Pequeña</x:v>
+      </x:c>
+      <x:c r="M31" s="20" t="str">
+        <x:f>Despiece!E31&amp;" × "&amp;Despiece!F31</x:f>
+        <x:v>2050 × 100</x:v>
+      </x:c>
+      <x:c r="N31" s="54" t="str">
+        <x:f>IF(LEN(TRIM(IF($L31="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M31,2)&amp;" × "&amp;ROUND(Despiece!N31,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A31,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L31="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M31,2)&amp;" × "&amp;ROUND(Despiece!N31,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A31,$S$2:$T$40,2,FALSE),"")))</x:f>
+        <x:v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo izquierdo libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="110" customHeight="1">
+      <x:c r="A32" s="20" t="str">
+        <x:f>Despiece!A32</x:f>
+        <x:v>C3-028</x:v>
+      </x:c>
+      <x:c r="B32" s="20" t="str">
+        <x:f>Despiece!B32</x:f>
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="C32" s="20" t="str">
+        <x:f>Despiece!C32</x:f>
+        <x:v>Montante posterior izquierdo</x:v>
+      </x:c>
+      <x:c r="D32" s="20" t="str">
+        <x:f>"RH15 Cartagena "&amp;Despiece!G32&amp;" mm"</x:f>
+        <x:v>RH15 Cartagena 15 mm</x:v>
+      </x:c>
+      <x:c r="E32" s="20" t="n">
+        <x:f>Despiece!D32</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F32" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!M32,2),Despiece!E32)</x:f>
+        <x:v>2050</x:v>
+      </x:c>
+      <x:c r="G32" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!N32,2),Despiece!F32)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H32" s="21" t="str">
+        <x:f>IF(Despiece!I32="2","R",IF(Despiece!I32="0.45","F","—"))</x:f>
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I32" s="21" t="str">
+        <x:f>IF(Despiece!J32="2","R",IF(Despiece!J32="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J32" s="21" t="str">
+        <x:f>IF(Despiece!K32="2","R",IF(Despiece!K32="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K32" s="21" t="str">
+        <x:f>IF(Despiece!L32="2","R",IF(Despiece!L32="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L32" s="21" t="str">
+        <x:f>IF(SUMPRODUCT((Despiece!I32:L32="2")+(Despiece!I32:L32="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M32,Despiece!N32)&lt;$Q$3,MAX(Despiece!M32,Despiece!N32)&lt;$Q$4),"Pequeña","Normal"))</x:f>
+        <x:v>Pequeña</x:v>
+      </x:c>
+      <x:c r="M32" s="20" t="str">
+        <x:f>Despiece!E32&amp;" × "&amp;Despiece!F32</x:f>
+        <x:v>2050 × 100</x:v>
+      </x:c>
+      <x:c r="N32" s="54" t="str">
+        <x:f>IF(LEN(TRIM(IF($L32="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M32,2)&amp;" × "&amp;ROUND(Despiece!N32,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A32,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L32="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M32,2)&amp;" × "&amp;ROUND(Despiece!N32,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A32,$S$2:$T$40,2,FALSE),"")))</x:f>
+        <x:v>Si no la cantean: cortar a 2050 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo derecho libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="110" customHeight="1">
+      <x:c r="A33" s="20" t="str">
+        <x:f>Despiece!A33</x:f>
+        <x:v>C3-029</x:v>
+      </x:c>
+      <x:c r="B33" s="20" t="str">
+        <x:f>Despiece!B33</x:f>
+        <x:v>B1</x:v>
+      </x:c>
+      <x:c r="C33" s="20" t="str">
+        <x:f>Despiece!C33</x:f>
+        <x:v>Amarre posterior inferior izquierdo</x:v>
+      </x:c>
+      <x:c r="D33" s="20" t="str">
+        <x:f>"RH15 Cartagena "&amp;Despiece!G33&amp;" mm"</x:f>
+        <x:v>RH15 Cartagena 15 mm</x:v>
+      </x:c>
+      <x:c r="E33" s="20" t="n">
+        <x:f>Despiece!D33</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F33" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!M33,2),Despiece!E33)</x:f>
+        <x:v>830</x:v>
+      </x:c>
+      <x:c r="G33" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!N33,2),Despiece!F33)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H33" s="21" t="str">
+        <x:f>IF(Despiece!I33="2","R",IF(Despiece!I33="0.45","F","—"))</x:f>
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I33" s="21" t="str">
+        <x:f>IF(Despiece!J33="2","R",IF(Despiece!J33="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J33" s="21" t="str">
+        <x:f>IF(Despiece!K33="2","R",IF(Despiece!K33="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K33" s="21" t="str">
+        <x:f>IF(Despiece!L33="2","R",IF(Despiece!L33="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L33" s="21" t="str">
+        <x:f>IF(SUMPRODUCT((Despiece!I33:L33="2")+(Despiece!I33:L33="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M33,Despiece!N33)&lt;$Q$3,MAX(Despiece!M33,Despiece!N33)&lt;$Q$4),"Pequeña","Normal"))</x:f>
+        <x:v>Pequeña</x:v>
+      </x:c>
+      <x:c r="M33" s="20" t="str">
+        <x:f>Despiece!E33&amp;" × "&amp;Despiece!F33</x:f>
+        <x:v>830 × 100</x:v>
+      </x:c>
+      <x:c r="N33" s="54" t="str">
+        <x:f>IF(LEN(TRIM(IF($L33="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M33,2)&amp;" × "&amp;ROUND(Despiece!N33,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A33,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L33="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M33,2)&amp;" × "&amp;ROUND(Despiece!N33,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A33,$S$2:$T$40,2,FALSE),"")))</x:f>
+        <x:v>Si no la cantean: cortar a 830 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="110" customHeight="1">
+      <x:c r="A34" s="20" t="str">
+        <x:f>Despiece!A34</x:f>
+        <x:v>C3-030</x:v>
+      </x:c>
+      <x:c r="B34" s="20" t="str">
+        <x:f>Despiece!B34</x:f>
+        <x:v>B2</x:v>
+      </x:c>
+      <x:c r="C34" s="20" t="str">
+        <x:f>Despiece!C34</x:f>
+        <x:v>Amarre posterior inferior derecho</x:v>
+      </x:c>
+      <x:c r="D34" s="20" t="str">
+        <x:f>"RH15 Cartagena "&amp;Despiece!G34&amp;" mm"</x:f>
+        <x:v>RH15 Cartagena 15 mm</x:v>
+      </x:c>
+      <x:c r="E34" s="20" t="n">
+        <x:f>Despiece!D34</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="F34" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!M34,2),Despiece!E34)</x:f>
+        <x:v>1075</x:v>
+      </x:c>
+      <x:c r="G34" s="31" t="n">
+        <x:f>IF($Q$2="NO",ROUND(Despiece!N34,2),Despiece!F34)</x:f>
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H34" s="21" t="str">
+        <x:f>IF(Despiece!I34="2","R",IF(Despiece!I34="0.45","F","—"))</x:f>
+        <x:v>F</x:v>
+      </x:c>
+      <x:c r="I34" s="21" t="str">
+        <x:f>IF(Despiece!J34="2","R",IF(Despiece!J34="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="J34" s="21" t="str">
+        <x:f>IF(Despiece!K34="2","R",IF(Despiece!K34="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="K34" s="21" t="str">
+        <x:f>IF(Despiece!L34="2","R",IF(Despiece!L34="0.45","F","—"))</x:f>
+        <x:v>—</x:v>
+      </x:c>
+      <x:c r="L34" s="21" t="str">
+        <x:f>IF(SUMPRODUCT((Despiece!I34:L34="2")+(Despiece!I34:L34="0.45"))=0,"Sin canto",IF(OR(MIN(Despiece!M34,Despiece!N34)&lt;$Q$3,MAX(Despiece!M34,Despiece!N34)&lt;$Q$4),"Pequeña","Normal"))</x:f>
+        <x:v>Pequeña</x:v>
+      </x:c>
+      <x:c r="M34" s="20" t="str">
+        <x:f>Despiece!E34&amp;" × "&amp;Despiece!F34</x:f>
+        <x:v>1075 × 100</x:v>
+      </x:c>
+      <x:c r="N34" s="54" t="str">
+        <x:f>IF(LEN(TRIM(IF($L34="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M34,2)&amp;" × "&amp;ROUND(Despiece!N34,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A34,$S$2:$T$40,2,FALSE),"")))=0,"—",TRIM(IF($L34="Pequeña","Si no la cantean: cortar a "&amp;ROUND(Despiece!M34,2)&amp;" × "&amp;ROUND(Despiece!N34,2)&amp;" y cantear en el armado.","")&amp;" "&amp;IFERROR(VLOOKUP(Despiece!A34,$S$2:$T$40,2,FALSE),"")))</x:f>
+        <x:v>Si no la cantean: cortar a 1075 × 99.55 y cantear en el armado. Marco posterior RH15 sin panel de fondo. Flexible 0,45 mm solo en el borde largo superior libre hacia el interior; los otros tres bordes son uniones ocultas sin canto. Unir a la caja y al resto del marco. Anclajes al muro posterior resistente y al izquierdo por dimensionar; no fijar solo al estuco.</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
-      <x:c r="C35" s="16" t="s">
-        <x:v>111</x:v>
-      </x:c>
+      <x:c r="A35"/>
+      <x:c r="B35"/>
+      <x:c r="C35" s="16"/>
       <x:c r="D35" s="23"/>
       <x:c r="E35" s="23"/>
-      <x:c r="F35" s="25" t="n">
-        <x:f>SUMPRODUCT($E$7:$E$30,--($L$7:$L$30&lt;&gt;"Pequeña"))</x:f>
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G35" s="25" t="n">
-        <x:f>SUMIF($L$7:$L$30,"Pequeña",$E$7:$E$30)</x:f>
-        <x:v>12</x:v>
-      </x:c>
+      <x:c r="F35" s="25"/>
+      <x:c r="G35" s="25"/>
+      <x:c r="H35"/>
+      <x:c r="I35"/>
+      <x:c r="J35"/>
+      <x:c r="K35"/>
+      <x:c r="L35"/>
+      <x:c r="M35"/>
+      <x:c r="N35"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36"/>
+      <x:c r="B36"/>
+      <x:c r="C36" s="16" t="str">
+        <x:v>Metros netos de canto</x:v>
+      </x:c>
+      <x:c r="D36" s="23"/>
+      <x:c r="E36" s="23"/>
+      <x:c r="F36" s="16" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="G36" s="16" t="str">
+        <x:v>Pequeña</x:v>
+      </x:c>
+      <x:c r="H36"/>
+      <x:c r="I36"/>
+      <x:c r="J36"/>
+      <x:c r="K36"/>
+      <x:c r="L36"/>
+      <x:c r="M36"/>
+      <x:c r="N36"/>
     </x:row>
     <x:row r="37">
-      <x:c r="C37" s="16" t="s">
-        <x:v>112</x:v>
+      <x:c r="A37"/>
+      <x:c r="B37"/>
+      <x:c r="C37" s="16" t="str">
+        <x:v>Rígido 2 mm</x:v>
       </x:c>
       <x:c r="D37" s="23"/>
       <x:c r="E37" s="23"/>
-      <x:c r="F37" s="16" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="G37" s="16" t="s">
-        <x:v>110</x:v>
-      </x:c>
+      <x:c r="F37" s="24" t="n">
+        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$E$7:$E$34,(Despiece!$I$7:$I$34="2")+(Despiece!$J$7:$J$34="2"),--($L$7:$L$34="Normal"))+SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$F$7:$F$34,(Despiece!$K$7:$K$34="2")+(Despiece!$L$7:$L$34="2"),--($L$7:$L$34="Normal")))/1000</x:f>
+        <x:v>18.804</x:v>
+      </x:c>
+      <x:c r="G37" s="24" t="n">
+        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$E$7:$E$34,(Despiece!$I$7:$I$34="2")+(Despiece!$J$7:$J$34="2"),--($L$7:$L$34="Pequeña"))+SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$F$7:$F$34,(Despiece!$K$7:$K$34="2")+(Despiece!$L$7:$L$34="2"),--($L$7:$L$34="Pequeña")))/1000</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H37"/>
+      <x:c r="I37"/>
+      <x:c r="J37"/>
+      <x:c r="K37"/>
+      <x:c r="L37"/>
+      <x:c r="M37"/>
+      <x:c r="N37"/>
     </x:row>
     <x:row r="38">
-      <x:c r="C38" s="14" t="s">
-        <x:v>113</x:v>
-      </x:c>
-      <x:c r="F38" s="27" t="n">
-        <x:f>SUMPRODUCT(Despiece!$D$7:$D$30,(Despiece!$I$7:$I$30="2")+(Despiece!$J$7:$J$30="2")+(Despiece!$K$7:$K$30="2")+(Despiece!$L$7:$L$30="2"),--($L$7:$L$30="Pequeña"))</x:f>
+      <x:c r="A38"/>
+      <x:c r="B38"/>
+      <x:c r="C38" s="16" t="str">
+        <x:v>Flexible 0,45 mm</x:v>
+      </x:c>
+      <x:c r="D38" s="23"/>
+      <x:c r="E38" s="23"/>
+      <x:c r="F38" s="24" t="n">
+        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$E$7:$E$34,(Despiece!$I$7:$I$34="0.45")+(Despiece!$J$7:$J$34="0.45"),--($L$7:$L$34="Normal"))+SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$F$7:$F$34,(Despiece!$K$7:$K$34="0.45")+(Despiece!$L$7:$L$34="0.45"),--($L$7:$L$34="Normal")))/1000</x:f>
+        <x:v>33.922</x:v>
+      </x:c>
+      <x:c r="G38" s="24" t="n">
+        <x:f>(SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$E$7:$E$34,(Despiece!$I$7:$I$34="0.45")+(Despiece!$J$7:$J$34="0.45"),--($L$7:$L$34="Pequeña"))+SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$F$7:$F$34,(Despiece!$K$7:$K$34="0.45")+(Despiece!$L$7:$L$34="0.45"),--($L$7:$L$34="Pequeña")))/1000</x:f>
+        <x:v>25.873</x:v>
+      </x:c>
+      <x:c r="H38"/>
+      <x:c r="I38"/>
+      <x:c r="J38"/>
+      <x:c r="K38"/>
+      <x:c r="L38"/>
+      <x:c r="M38"/>
+      <x:c r="N38"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39"/>
+      <x:c r="B39"/>
+      <x:c r="C39" s="16" t="str">
+        <x:v>Piezas (unidades)</x:v>
+      </x:c>
+      <x:c r="D39" s="23"/>
+      <x:c r="E39" s="23"/>
+      <x:c r="F39" s="25" t="n">
+        <x:f>SUMPRODUCT($E$7:$E$34,--($L$7:$L$34&lt;&gt;"Pequeña"))</x:f>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G39" s="25" t="n">
+        <x:f>SUMIF($L$7:$L$34,"Pequeña",$E$7:$E$34)</x:f>
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H39"/>
+      <x:c r="I39"/>
+      <x:c r="J39"/>
+      <x:c r="K39"/>
+      <x:c r="L39"/>
+      <x:c r="M39"/>
+      <x:c r="N39"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40"/>
+      <x:c r="B40"/>
+      <x:c r="C40"/>
+      <x:c r="D40"/>
+      <x:c r="E40"/>
+      <x:c r="F40"/>
+      <x:c r="G40"/>
+      <x:c r="H40"/>
+      <x:c r="I40"/>
+      <x:c r="J40"/>
+      <x:c r="K40"/>
+      <x:c r="L40"/>
+      <x:c r="M40"/>
+      <x:c r="N40"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41"/>
+      <x:c r="B41"/>
+      <x:c r="C41" s="16" t="str">
+        <x:v>Canto para acabado manual · previsión sujeta a la entrega</x:v>
+      </x:c>
+      <x:c r="D41" s="23"/>
+      <x:c r="E41" s="23"/>
+      <x:c r="F41" s="16" t="str">
+        <x:v>Rígido 2 mm</x:v>
+      </x:c>
+      <x:c r="G41" s="16" t="str">
+        <x:v>Flexible 0,45 mm</x:v>
+      </x:c>
+      <x:c r="H41"/>
+      <x:c r="I41"/>
+      <x:c r="J41"/>
+      <x:c r="K41"/>
+      <x:c r="L41"/>
+      <x:c r="M41"/>
+      <x:c r="N41"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42"/>
+      <x:c r="B42"/>
+      <x:c r="C42" s="14" t="str">
+        <x:v>Bordes a cantear a mano</x:v>
+      </x:c>
+      <x:c r="D42"/>
+      <x:c r="E42"/>
+      <x:c r="F42" s="27" t="n">
+        <x:f>SUMPRODUCT(Despiece!$D$7:$D$34,(Despiece!$I$7:$I$34="2")+(Despiece!$J$7:$J$34="2")+(Despiece!$K$7:$K$34="2")+(Despiece!$L$7:$L$34="2"),--($L$7:$L$34="Pequeña"))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G38" s="27" t="n">
-        <x:f>SUMPRODUCT(Despiece!$D$7:$D$30,(Despiece!$I$7:$I$30="0.45")+(Despiece!$J$7:$J$30="0.45")+(Despiece!$K$7:$K$30="0.45")+(Despiece!$L$7:$L$30="0.45"),--($L$7:$L$30="Pequeña"))</x:f>
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39">
-      <x:c r="C39" s="14" t="s">
-        <x:v>114</x:v>
-      </x:c>
-      <x:c r="F39" s="28" t="n">
-        <x:f>G33</x:f>
+      <x:c r="G42" s="27" t="n">
+        <x:f>SUMPRODUCT(Despiece!$D$7:$D$34,(Despiece!$I$7:$I$34="0.45")+(Despiece!$J$7:$J$34="0.45")+(Despiece!$K$7:$K$34="0.45")+(Despiece!$L$7:$L$34="0.45"),--($L$7:$L$34="Pequeña"))</x:f>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="H42"/>
+      <x:c r="I42"/>
+      <x:c r="J42"/>
+      <x:c r="K42"/>
+      <x:c r="L42"/>
+      <x:c r="M42"/>
+      <x:c r="N42"/>
+    </x:row>
+    <x:row r="43" ht="49.95000076293945" customHeight="1">
+      <x:c r="A43"/>
+      <x:c r="B43"/>
+      <x:c r="C43" s="14" t="str">
+        <x:v>Metros netos</x:v>
+      </x:c>
+      <x:c r="D43"/>
+      <x:c r="E43"/>
+      <x:c r="F43" s="28" t="n">
+        <x:f>G37</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G39" s="28" t="n">
-        <x:f>G34</x:f>
-        <x:v>17.963</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40">
-      <x:c r="C40" s="14" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="F40" s="29">
+      <x:c r="G43" s="28" t="n">
+        <x:f>G38</x:f>
+        <x:v>25.873</x:v>
+      </x:c>
+      <x:c r="H43"/>
+      <x:c r="I43"/>
+      <x:c r="J43"/>
+      <x:c r="K43"/>
+      <x:c r="L43"/>
+      <x:c r="M43"/>
+      <x:c r="N43"/>
+    </x:row>
+    <x:row r="44" ht="34.04999923706055" customHeight="1">
+      <x:c r="A44"/>
+      <x:c r="B44"/>
+      <x:c r="C44" s="14" t="str">
+        <x:v>Desperdicio por borde a mano (m)</x:v>
+      </x:c>
+      <x:c r="D44"/>
+      <x:c r="E44"/>
+      <x:c r="F44" s="50" t="n">
         <x:v>0.1</x:v>
       </x:c>
-      <x:c r="G40" s="29">
+      <x:c r="G44" s="50" t="n">
         <x:v>0.1</x:v>
       </x:c>
-    </x:row>
-    <x:row r="41">
-      <x:c r="C41" s="14" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="F41" s="30">
+      <x:c r="H44"/>
+      <x:c r="I44"/>
+      <x:c r="J44"/>
+      <x:c r="K44"/>
+      <x:c r="L44"/>
+      <x:c r="M44"/>
+      <x:c r="N44"/>
+    </x:row>
+    <x:row r="45" ht="34.04999923706055" customHeight="1">
+      <x:c r="A45"/>
+      <x:c r="B45"/>
+      <x:c r="C45" s="14" t="str">
+        <x:v>Margen de seguridad</x:v>
+      </x:c>
+      <x:c r="D45"/>
+      <x:c r="E45"/>
+      <x:c r="F45" s="49" t="n">
         <x:v>0.2</x:v>
       </x:c>
-      <x:c r="G41" s="30">
+      <x:c r="G45" s="49" t="n">
         <x:v>0.2</x:v>
       </x:c>
-    </x:row>
-    <x:row r="42">
-      <x:c r="C42" s="16" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="D42" s="23"/>
-      <x:c r="E42" s="23"/>
-      <x:c r="F42" s="26" t="n">
-        <x:f>IF(F38=0,0,ROUNDUP((F39+F38*F40)*(1+F41),0))</x:f>
+      <x:c r="H45"/>
+      <x:c r="I45"/>
+      <x:c r="J45"/>
+      <x:c r="K45"/>
+      <x:c r="L45"/>
+      <x:c r="M45"/>
+      <x:c r="N45"/>
+    </x:row>
+    <x:row r="46" ht="34.04999923706055" customHeight="1">
+      <x:c r="A46"/>
+      <x:c r="B46"/>
+      <x:c r="C46" s="16" t="str">
+        <x:v>Estimado con desperdicio y reserva (m)</x:v>
+      </x:c>
+      <x:c r="D46" s="23"/>
+      <x:c r="E46" s="23"/>
+      <x:c r="F46" s="48" t="n">
+        <x:f>IF(F42=0,0,ROUNDUP((F43+F42*F44)*(1+F45),0))</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G42" s="26" t="n">
-        <x:f>IF(G38=0,0,ROUNDUP((G39+G38*G40)*(1+G41),0))</x:f>
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="49.95000076293945" customHeight="1">
-      <x:c r="C43" s="39" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D43" s="40"/>
-      <x:c r="E43" s="40"/>
-      <x:c r="F43" s="40"/>
-      <x:c r="G43" s="40"/>
-      <x:c r="H43" s="40"/>
-      <x:c r="I43" s="40"/>
-      <x:c r="J43" s="40"/>
-      <x:c r="K43" s="40"/>
-      <x:c r="L43" s="40"/>
-      <x:c r="M43" s="40"/>
-      <x:c r="N43" s="40"/>
-    </x:row>
-    <x:row r="44" ht="34.04999923706055" customHeight="1">
-      <x:c r="C44" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="F44" s="32"/>
-      <x:c r="G44" s="32"/>
-    </x:row>
-    <x:row r="45" ht="34.04999923706055" customHeight="1">
-      <x:c r="C45" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F45" s="32">
+      <x:c r="G46" s="48" t="n">
+        <x:f>IF(G42=0,0,ROUNDUP((G43+G42*G44)*(1+G45),0))</x:f>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H46"/>
+      <x:c r="I46"/>
+      <x:c r="J46"/>
+      <x:c r="K46"/>
+      <x:c r="L46"/>
+      <x:c r="M46"/>
+      <x:c r="N46"/>
+    </x:row>
+    <x:row r="47" ht="49.95000076293945" customHeight="1">
+      <x:c r="A47"/>
+      <x:c r="B47"/>
+      <x:c r="C47" s="39" t="str">
+        <x:v>Previsión para las piezas pequeñas, no garantía de cuáles canteará Madecentro. Incluye 10 cm extra por borde y 20 % de reserva; ambos valores son editables. Al recibir las piezas, ajustar el objetivo si faltan otros bordes o si el proveedor canteó parte de ellos.</x:v>
+      </x:c>
+      <x:c r="D47"/>
+      <x:c r="E47"/>
+      <x:c r="F47"/>
+      <x:c r="G47"/>
+      <x:c r="H47"/>
+      <x:c r="I47"/>
+      <x:c r="J47"/>
+      <x:c r="K47"/>
+      <x:c r="L47"/>
+      <x:c r="M47"/>
+      <x:c r="N47"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48"/>
+      <x:c r="B48"/>
+      <x:c r="C48" t="str">
+        <x:v>Objetivo revisado con reserva (m; opcional)</x:v>
+      </x:c>
+      <x:c r="D48"/>
+      <x:c r="E48"/>
+      <x:c r="F48" s="47"/>
+      <x:c r="G48" s="47"/>
+      <x:c r="H48"/>
+      <x:c r="I48"/>
+      <x:c r="J48"/>
+      <x:c r="K48"/>
+      <x:c r="L48"/>
+      <x:c r="M48"/>
+      <x:c r="N48"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49"/>
+      <x:c r="B49"/>
+      <x:c r="C49" t="str">
+        <x:v>Metros ya disponibles para cantear en casa</x:v>
+      </x:c>
+      <x:c r="D49"/>
+      <x:c r="E49"/>
+      <x:c r="F49" s="47" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G45" s="32">
+      <x:c r="G49" s="47" t="n">
         <x:v>0</x:v>
       </x:c>
-    </x:row>
-    <x:row r="46" ht="34.04999923706055" customHeight="1">
-      <x:c r="C46" s="33" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="D46" s="33"/>
-      <x:c r="E46" s="33"/>
-      <x:c r="F46" s="34" t="n">
-        <x:f>ROUNDUP(MAX(IF(ISNUMBER(F44),F44,F42)-F45,0),0)</x:f>
+      <x:c r="H49"/>
+      <x:c r="I49"/>
+      <x:c r="J49"/>
+      <x:c r="K49"/>
+      <x:c r="L49"/>
+      <x:c r="M49"/>
+      <x:c r="N49"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50"/>
+      <x:c r="B50"/>
+      <x:c r="C50" s="45" t="str">
+        <x:v>Metros faltantes por comprar</x:v>
+      </x:c>
+      <x:c r="D50" s="45"/>
+      <x:c r="E50" s="45"/>
+      <x:c r="F50" s="46" t="n">
+        <x:f>ROUNDUP(MAX(IF(ISNUMBER(F48),F48,F46)-F49,0),0)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G46" s="34" t="n">
-        <x:f>ROUNDUP(MAX(IF(ISNUMBER(G44),G44,G42)-G45,0),0)</x:f>
-        <x:v>26</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" ht="49.95000076293945" customHeight="1">
-      <x:c r="C47" s="41" t="s">
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D47" s="40"/>
-      <x:c r="E47" s="40"/>
-      <x:c r="F47" s="40"/>
-      <x:c r="G47" s="40"/>
-      <x:c r="H47" s="40"/>
-      <x:c r="I47" s="40"/>
-      <x:c r="J47" s="40"/>
-      <x:c r="K47" s="40"/>
-      <x:c r="L47" s="40"/>
-      <x:c r="M47" s="40"/>
-      <x:c r="N47" s="40"/>
+      <x:c r="G50" s="46" t="n">
+        <x:f>ROUNDUP(MAX(IF(ISNUMBER(G48),G48,G46)-G49,0),0)</x:f>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="H50"/>
+      <x:c r="I50"/>
+      <x:c r="J50"/>
+      <x:c r="K50"/>
+      <x:c r="L50"/>
+      <x:c r="M50"/>
+      <x:c r="N50"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51"/>
+      <x:c r="B51"/>
+      <x:c r="C51" s="41" t="str">
+        <x:v>Dejar el objetivo revisado vacío para usar el estimado. Si ya hay canto comprado o sobrante de rollos, anotarlo en metros disponibles. No sumar este material dos veces al presupuesto. Precio por metro suelto y pegante por cotizar con el proveedor.</x:v>
+      </x:c>
+      <x:c r="D51"/>
+      <x:c r="E51"/>
+      <x:c r="F51"/>
+      <x:c r="G51"/>
+      <x:c r="H51"/>
+      <x:c r="I51"/>
+      <x:c r="J51"/>
+      <x:c r="K51"/>
+      <x:c r="L51"/>
+      <x:c r="M51"/>
+      <x:c r="N51"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="C43:N43"/>
     <x:mergeCell ref="C47:N47"/>
+    <x:mergeCell ref="C51:N51"/>
   </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q2"/>
@@ -4642,7 +5176,7 @@
     </x:row>
     <x:row r="2" ht="19.5" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -4656,7 +5190,7 @@
     </x:row>
     <x:row r="3" ht="15" customHeight="1">
       <x:c r="A3" s="12" t="s">
-        <x:v>124</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -4668,9 +5202,9 @@
       <x:c r="I3" s="1"/>
       <x:c r="J3" s="1"/>
     </x:row>
-    <x:row r="4" ht="15" customHeight="1">
-      <x:c r="A4" s="1" t="s">
-        <x:v>125</x:v>
+    <x:row r="4" ht="100" customHeight="1">
+      <x:c r="A4" s="43" t="str">
+        <x:v>Encaje individual encontrado en 4 láminas, con veta fija, sierra 5 mm y refilado 10 mm por lado. No es plano definitivo ni mínimo demostrado.</x:v>
       </x:c>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1"/>
@@ -4696,78 +5230,78 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>126</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>127</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>128</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>130</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>132</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I6" s="1"/>
       <x:c r="J6" s="1" t="s">
-        <x:v>133</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="79.5" customHeight="1">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="100" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>135</x:v>
-      </x:c>
-      <x:c r="C7" s="1">
-        <x:v>5</x:v>
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C7" s="1" t="n">
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E7" s="9">
         <x:v>365872</x:v>
       </x:c>
       <x:c r="F7" s="9" t="n">
         <x:f t="shared" ref="F7:F21" si="0">IF(COUNT(C7,E7)=2,C7*E7,"Por cotizar")</x:f>
-        <x:v>1829360</x:v>
+        <x:v>1463488</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>137</x:v>
-      </x:c>
-      <x:c r="H7" s="4" t="s">
-        <x:v>138</x:v>
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H7" s="43" t="str">
+        <x:v>48 piezas RH15, 15.501170 m² netos. Sin panel trasero: C3-025 a C3-030 forman el marco posterior completo. Compra conjunta en compras-proyecto.xlsx.</x:v>
       </x:c>
       <x:c r="I7" s="12"/>
       <x:c r="J7" s="13" t="s">
-        <x:v>139</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="79.5" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C8" s="1" t="n">
         <x:f>Cantos!H7</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E8" s="9">
         <x:v>531600</x:v>
@@ -4777,29 +5311,29 @@
         <x:v>531600</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H8" s="4" t="s">
-        <x:v>144</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I8" s="1"/>
       <x:c r="J8" s="13" t="s">
-        <x:v>145</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="79.5" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>147</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C9" s="1" t="n">
         <x:f>Cantos!H8</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="E9" s="9">
         <x:v>285600</x:v>
@@ -4809,28 +5343,28 @@
         <x:v>285600</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="H9" s="4" t="str">
         <x:v>Metraje actualizado en Cantos y compras-proyecto.xlsx. Confirmar decorativo compatible y canteado de piezas estrechas. Para acabado manual, registrar la entrega real y descontar metros disponibles.</x:v>
       </x:c>
       <x:c r="I9" s="1"/>
       <x:c r="J9" s="13" t="s">
-        <x:v>145</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="79.5" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>149</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C10" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E10" s="9">
         <x:v>11287</x:v>
@@ -4840,28 +5374,28 @@
         <x:v>33861</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H10" s="13" t="s">
-        <x:v>152</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="I10" s="12"/>
       <x:c r="J10" s="13" t="s">
-        <x:v>153</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="79.5" customHeight="1">
       <x:c r="A11" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B11" s="4" t="s">
-        <x:v>155</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C11" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="E11" s="9">
         <x:v>12730</x:v>
@@ -4871,28 +5405,28 @@
         <x:v>12730</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>157</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="H11" s="4" t="s">
-        <x:v>158</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="I11" s="1"/>
       <x:c r="J11" s="4" t="s">
-        <x:v>159</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="79.5" customHeight="1">
       <x:c r="A12" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B12" s="4" t="s">
-        <x:v>161</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C12" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E12" s="9">
         <x:v>33278</x:v>
@@ -4902,28 +5436,28 @@
         <x:v>33278</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>151</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="H12" s="4" t="s">
-        <x:v>163</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="I12" s="1"/>
       <x:c r="J12" s="4" t="s">
-        <x:v>164</x:v>
+        <x:v>137</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="79.5" customHeight="1">
       <x:c r="A13" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B13" s="4" t="s">
-        <x:v>166</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="C13" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E13" s="9">
         <x:v>2743</x:v>
@@ -4933,26 +5467,26 @@
         <x:v>5486</x:v>
       </x:c>
       <x:c r="G13" s="13" t="s">
-        <x:v>168</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H13" s="4" t="s">
-        <x:v>169</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="I13" s="1"/>
       <x:c r="J13" s="4" t="s">
-        <x:v>170</x:v>
+        <x:v>143</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="79.5" customHeight="1">
       <x:c r="A14" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B14" s="4" t="s">
-        <x:v>172</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="C14" s="1"/>
       <x:c r="D14" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="E14" s="9"/>
       <x:c r="F14" s="9" t="str">
@@ -4960,28 +5494,28 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G14" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="H14" s="4" t="s">
-        <x:v>175</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="I14" s="1"/>
       <x:c r="J14" s="4" t="s">
-        <x:v>176</x:v>
+        <x:v>149</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="79.5" customHeight="1">
       <x:c r="A15" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B15" s="4" t="s">
-        <x:v>178</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C15" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E15" s="9"/>
       <x:c r="F15" s="9" t="str">
@@ -4989,28 +5523,28 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G15" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H15" s="4" t="s">
-        <x:v>181</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I15" s="1"/>
       <x:c r="J15" s="4" t="s">
-        <x:v>182</x:v>
+        <x:v>155</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="79.5" customHeight="1">
       <x:c r="A16" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B16" s="4" t="s">
-        <x:v>183</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C16" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E16" s="9"/>
       <x:c r="F16" s="9" t="str">
@@ -5018,28 +5552,28 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G16" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H16" s="4" t="s">
-        <x:v>184</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="I16" s="1"/>
       <x:c r="J16" s="4" t="s">
-        <x:v>185</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="79.5" customHeight="1">
       <x:c r="A17" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B17" s="4" t="s">
-        <x:v>187</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C17" s="1">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="E17" s="9"/>
       <x:c r="F17" s="9" t="str">
@@ -5047,28 +5581,28 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G17" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H17" s="4" t="s">
-        <x:v>188</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="I17" s="1"/>
       <x:c r="J17" s="4" t="s">
-        <x:v>189</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="79.5" customHeight="1">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="100" customHeight="1">
       <x:c r="A18" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B18" s="4" t="s">
-        <x:v>190</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C18" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E18" s="9"/>
       <x:c r="F18" s="9" t="str">
@@ -5076,28 +5610,28 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G18" s="4" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H18" s="13" t="s">
-        <x:v>192</x:v>
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H18" s="42" t="str">
+        <x:v>Unir el marco completo C3-025 a C3-030 a laterales, divisor, pisos y tapas. Dimensionar anclajes al muro posterior resistente y al izquierdo. No fijar solo al estuco. El lateral derecho queda libre: el montante se une a la caja y al muro de fondo, no a una pared lateral inexistente. El marco abierto no se da por equivalente a un panel arriostrante.</x:v>
       </x:c>
       <x:c r="I18" s="1"/>
       <x:c r="J18" s="4" t="s">
-        <x:v>193</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="79.5" customHeight="1">
       <x:c r="A19" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="B19" s="4" t="s">
-        <x:v>195</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C19" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E19" s="9"/>
       <x:c r="F19" s="9" t="str">
@@ -5105,28 +5639,28 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G19" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H19" s="4" t="s">
-        <x:v>197</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="I19" s="1"/>
       <x:c r="J19" s="4" t="s">
-        <x:v>198</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="79.5" customHeight="1">
       <x:c r="A20" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B20" s="4" t="s">
-        <x:v>199</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C20" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="E20" s="9"/>
       <x:c r="F20" s="9" t="str">
@@ -5134,28 +5668,28 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G20" s="4" t="s">
-        <x:v>180</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="H20" s="4" t="s">
-        <x:v>200</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="I20" s="1"/>
       <x:c r="J20" s="4" t="s">
-        <x:v>185</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="79.5" customHeight="1">
+        <x:v>158</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="100" customHeight="1">
       <x:c r="A21" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B21" s="4" t="s">
-        <x:v>202</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C21" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="E21" s="9"/>
       <x:c r="F21" s="9" t="str">
@@ -5163,19 +5697,19 @@
         <x:v>Por cotizar</x:v>
       </x:c>
       <x:c r="G21" s="4" t="s">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="H21" s="4" t="s">
-        <x:v>204</x:v>
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="H21" s="43" t="str">
+        <x:v>Canteado de las seis tiras solo en su borde libre interior; fijaciones y escuadrado de marco posterior abierto. Definir y ejecutar anclajes antes de usar las hojas. Confirmar mínimos y tolerancias.</x:v>
       </x:c>
       <x:c r="I21" s="1"/>
       <x:c r="J21" s="4" t="s">
-        <x:v>205</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="23.25" customHeight="1">
       <x:c r="A22" s="10" t="s">
-        <x:v>206</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B22" s="10"/>
       <x:c r="C22" s="10"/>
@@ -5183,11 +5717,11 @@
       <x:c r="E22" s="11"/>
       <x:c r="F22" s="11" t="n">
         <x:f>SUM(F7:F21)</x:f>
-        <x:v>2731915</x:v>
+        <x:v>2366043</x:v>
       </x:c>
       <x:c r="G22" s="10"/>
       <x:c r="H22" s="38" t="s">
-        <x:v>207</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="I22" s="1"/>
       <x:c r="J22" s="1"/>
@@ -5248,7 +5782,7 @@
     </x:row>
     <x:row r="2" ht="19.5" customHeight="1">
       <x:c r="A2" s="2" t="s">
-        <x:v>208</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="1"/>
@@ -5257,7 +5791,7 @@
       <x:c r="F2" s="1"/>
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="I2" s="1">
         <x:v>0.05</x:v>
@@ -5265,7 +5799,7 @@
     </x:row>
     <x:row r="3" ht="85" customHeight="1">
       <x:c r="A3" s="42" t="str">
-        <x:v>Un solo tipo de canto por pieza: rígido 2 mm en puertas/frentes de uso frecuente y terminal expuesto; flexible 0,45 mm en estructura e interiores. Se conservan los bordes protegidos y las medidas terminadas. El corte del tablero descuenta el espesor nuevo una sola vez. Reserva de 5 cm por borde.</x:v>
+        <x:v>Marco completo C3-025 a C3-030: flexible de 0,45 mm únicamente en el borde largo libre hacia el cuadro interior. Los otros tres bordes son uniones ocultas sin canto. El resto conserva su canteo aprobado. Medidas finales con canto incluido.</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -5300,44 +5834,44 @@
     </x:row>
     <x:row r="6" ht="42" customHeight="1">
       <x:c r="A6" s="3" t="s">
-        <x:v>210</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B6" s="3" t="s">
-        <x:v>211</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C6" s="3" t="s">
-        <x:v>114</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D6" s="3" t="s">
-        <x:v>212</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E6" s="3" t="s">
-        <x:v>213</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F6" s="3" t="s">
-        <x:v>214</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="G6" s="3" t="s">
-        <x:v>215</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="H6" s="3" t="s">
-        <x:v>216</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="I6" s="1"/>
     </x:row>
     <x:row r="7" ht="85" customHeight="1">
       <x:c r="A7" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B7" s="43" t="str">
         <x:v>Hojas corredizas y frentes de cajón</x:v>
       </x:c>
       <x:c r="C7" s="8" t="n">
-        <x:f>SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="2")+(Despiece!$J$7:$J$30="2"))/1000+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="2")+(Despiece!$L$7:$L$30="2"))/1000</x:f>
+        <x:f>SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$E$7:$E$34,(Despiece!$I$7:$I$34="2")+(Despiece!$J$7:$J$34="2"))/1000+SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$F$7:$F$34,(Despiece!$K$7:$K$34="2")+(Despiece!$L$7:$L$34="2"))/1000</x:f>
         <x:v>18.804000000000002</x:v>
       </x:c>
       <x:c r="D7" s="1" t="n">
-        <x:f>SUMPRODUCT(Despiece!$D$7:$D$30,(Despiece!$I$7:$I$30="2")+(Despiece!$J$7:$J$30="2")+(Despiece!$K$7:$K$30="2")+(Despiece!$L$7:$L$30="2"))</x:f>
+        <x:f>SUMPRODUCT(Despiece!$D$7:$D$34,(Despiece!$I$7:$I$34="2")+(Despiece!$J$7:$J$34="2")+(Despiece!$K$7:$K$34="2")+(Despiece!$L$7:$L$34="2"))</x:f>
         <x:v>20</x:v>
       </x:c>
       <x:c r="E7" s="6" t="n">
@@ -5359,26 +5893,26 @@
     </x:row>
     <x:row r="8" ht="85" customHeight="1">
       <x:c r="A8" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="B8" s="42" t="str">
         <x:v>Estructura, solapa, base y piezas interiores</x:v>
       </x:c>
       <x:c r="C8" s="8" t="n">
-        <x:f>SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$E$7:$E$30,(Despiece!$I$7:$I$30="0.45")+(Despiece!$J$7:$J$30="0.45"))/1000+SUMPRODUCT(Despiece!$D$7:$D$30,Despiece!$F$7:$F$30,(Despiece!$K$7:$K$30="0.45")+(Despiece!$L$7:$L$30="0.45"))/1000</x:f>
-        <x:v>51.885</x:v>
+        <x:f>SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$E$7:$E$34,(Despiece!$I$7:$I$34="0.45")+(Despiece!$J$7:$J$34="0.45"))/1000+SUMPRODUCT(Despiece!$D$7:$D$34,Despiece!$F$7:$F$34,(Despiece!$K$7:$K$34="0.45")+(Despiece!$L$7:$L$34="0.45"))/1000</x:f>
+        <x:v>59.795</x:v>
       </x:c>
       <x:c r="D8" s="1" t="n">
-        <x:f>SUMPRODUCT(Despiece!$D$7:$D$30,(Despiece!$I$7:$I$30="0.45")+(Despiece!$J$7:$J$30="0.45")+(Despiece!$K$7:$K$30="0.45")+(Despiece!$L$7:$L$30="0.45"))</x:f>
-        <x:v>80</x:v>
+        <x:f>SUMPRODUCT(Despiece!$D$7:$D$34,(Despiece!$I$7:$I$34="0.45")+(Despiece!$J$7:$J$34="0.45")+(Despiece!$K$7:$K$34="0.45")+(Despiece!$L$7:$L$34="0.45"))</x:f>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E8" s="6" t="n">
         <x:f>D8*$I$2</x:f>
-        <x:v>4</x:v>
+        <x:v>4.3</x:v>
       </x:c>
       <x:c r="F8" s="1" t="n">
         <x:f>ROUNDUP((C8+E8)/5,0)*5</x:f>
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G8" s="1">
         <x:v>200</x:v>
@@ -5402,7 +5936,7 @@
     </x:row>
     <x:row r="10" ht="15" customHeight="1">
       <x:c r="A10" s="12" t="s">
-        <x:v>219</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B10" s="1"/>
       <x:c r="C10" s="1"/>
@@ -5452,29 +5986,29 @@
   <x:sheetData>
     <x:row r="2" ht="17.399999618530273">
       <x:c r="A2" s="15" t="s">
-        <x:v>220</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="17" t="s">
-        <x:v>221</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="35" t="s">
-        <x:v>222</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="B6" s="35" t="s">
-        <x:v>223</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C6" s="35" t="s">
-        <x:v>224</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="D6" s="35" t="s">
-        <x:v>225</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="E6" s="35" t="s">
-        <x:v>226</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="26.399999618530273">
@@ -5482,33 +6016,33 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B7" s="37" t="s">
-        <x:v>227</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C7" s="37" t="s">
-        <x:v>228</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="D7" s="37" t="s">
-        <x:v>229</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="E7" s="37" t="s">
-        <x:v>230</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="26.399999618530273">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="100" customHeight="1">
       <x:c r="A8" s="36">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B8" s="37" t="s">
-        <x:v>231</x:v>
-      </x:c>
-      <x:c r="C8" s="37" t="s">
-        <x:v>232</x:v>
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="C8" s="44" t="str">
+        <x:v>Confirmar medida final con descuento de canto y mínimos de máquina. Encaje individual: 4 RH15. El PDF anterior con C3-005/C3-011 queda sustituido por el pedido del marco C3-025 a C3-030.</x:v>
       </x:c>
       <x:c r="D8" s="37" t="s">
-        <x:v>233</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E8" s="37" t="s">
-        <x:v>234</x:v>
+        <x:v>205</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273">
@@ -5516,16 +6050,16 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="B9" s="37" t="s">
-        <x:v>235</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C9" s="37" t="s">
-        <x:v>236</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D9" s="37" t="s">
-        <x:v>237</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E9" s="37" t="s">
-        <x:v>238</x:v>
+        <x:v>209</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="26.399999618530273">
@@ -5533,16 +6067,16 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="B10" s="37" t="s">
-        <x:v>239</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C10" s="37" t="s">
-        <x:v>240</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D10" s="37" t="s">
-        <x:v>241</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="E10" s="37" t="s">
-        <x:v>242</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -5550,33 +6084,33 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B11" s="37" t="s">
-        <x:v>243</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C11" s="37" t="s">
-        <x:v>244</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D11" s="37" t="s">
-        <x:v>245</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E11" s="37" t="s">
-        <x:v>246</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="26.399999618530273">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="100" customHeight="1">
       <x:c r="A12" s="36">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B12" s="37" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="C12" s="37" t="s">
-        <x:v>248</x:v>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="C12" s="44" t="str">
+        <x:v>Definir uniones del marco C3-025 a C3-030 y anclajes al muro posterior resistente y al izquierdo. El estuco es acabado, no soporte estructural. El extremo derecho no tiene pared lateral. Verificar escuadre y fijaciones antes de cargar o mover hojas colgantes; el marco abierto no garantiza por sí solo la rigidez de los paneles retirados.</x:v>
       </x:c>
       <x:c r="D12" s="37" t="s">
-        <x:v>249</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="E12" s="37" t="s">
-        <x:v>242</x:v>
+        <x:v>213</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273">
@@ -5584,16 +6118,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B13" s="37" t="s">
-        <x:v>250</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C13" s="37" t="s">
-        <x:v>251</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="D13" s="37" t="s">
-        <x:v>245</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E13" s="37" t="s">
-        <x:v>252</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="26.399999618530273">
@@ -5601,16 +6135,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B14" s="37" t="s">
-        <x:v>253</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C14" s="37" t="s">
-        <x:v>254</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D14" s="37" t="s">
-        <x:v>255</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E14" s="37" t="s">
-        <x:v>256</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -5629,133 +6163,144 @@
   <x:sheetData>
     <x:row r="2" ht="17.399999618530273">
       <x:c r="A2" s="15" t="s">
-        <x:v>257</x:v>
+        <x:v>227</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="17" t="s">
-        <x:v>258</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="35" t="s">
-        <x:v>223</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B6" s="35" t="s">
-        <x:v>259</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C6" s="35" t="s">
-        <x:v>260</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="37" t="s">
-        <x:v>261</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B7" s="37" t="s">
-        <x:v>262</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C7" s="37" t="s">
-        <x:v>263</x:v>
+        <x:v>233</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="39.599998474121094">
       <x:c r="A8" s="37" t="s">
-        <x:v>264</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="B8" s="37" t="s">
-        <x:v>265</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C8" s="37" t="s">
-        <x:v>266</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="26.399999618530273">
       <x:c r="A9" s="37" t="s">
-        <x:v>267</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B9" s="37" t="s">
-        <x:v>268</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C9" s="37" t="s">
-        <x:v>269</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="39.599998474121094">
+        <x:v>239</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="100" customHeight="1">
       <x:c r="A10" s="37" t="s">
-        <x:v>270</x:v>
-      </x:c>
-      <x:c r="B10" s="37" t="s">
-        <x:v>271</x:v>
+        <x:v>240</x:v>
+      </x:c>
+      <x:c r="B10" s="44" t="str">
+        <x:v>Se mantiene cuerpo de 560 mm, hojas y rieles en sus posiciones y hasta 585 mm con manijas. Sin panel trasero: las tiras nuevas ocupan la franja z=0–15 del respaldo anterior. No se adelanta el clóset ni se reducen vanos de cajones, guía o margen de giro.</x:v>
       </x:c>
       <x:c r="C10" s="37" t="s">
-        <x:v>272</x:v>
+        <x:v>241</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="39.599998474121094">
       <x:c r="A11" s="37" t="s">
-        <x:v>273</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="B11" s="37" t="s">
-        <x:v>274</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C11" s="37" t="s">
-        <x:v>275</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="52.79999923706055">
       <x:c r="A12" s="37" t="s">
-        <x:v>276</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B12" s="37" t="s">
-        <x:v>277</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C12" s="37" t="s">
-        <x:v>278</x:v>
+        <x:v>247</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="26.399999618530273">
       <x:c r="A13" s="37" t="s">
-        <x:v>279</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="B13" s="37" t="s">
-        <x:v>280</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="C13" s="37" t="s">
-        <x:v>281</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="26.399999618530273">
+        <x:v>250</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="100" customHeight="1">
       <x:c r="A14" s="37" t="s">
-        <x:v>282</x:v>
-      </x:c>
-      <x:c r="B14" s="37" t="s">
-        <x:v>283</x:v>
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="B14" s="44" t="str">
+        <x:v>Mismo RH15 Cartagena de cocina. El clóset se integra con cocina y baño en compras-proyecto.xlsx. Sin panel RH6 adicional y sin cambios de material en cocina o baño.</x:v>
       </x:c>
       <x:c r="C14" s="37" t="s">
-        <x:v>284</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="85" customHeight="1">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="100" customHeight="1">
       <x:c r="A15" s="37" t="s">
-        <x:v>285</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B15" s="44" t="str">
-        <x:v>Un solo tipo de canto por pieza: rígido 2 mm en puertas/frentes de uso frecuente y terminal expuesto; flexible 0,45 mm en estructura e interiores. Se conservan los bordes protegidos y las medidas terminadas. El corte del tablero descuenta el espesor nuevo una sola vez. Fondos RH15 sin canto; base C3-020 a C3-022 con flexible en los cuatro bordes.</x:v>
+        <x:v>Canteo aprobado del resto sin cambios. En las seis tiras posteriores solo se cantea el borde largo libre del cuadro interior, flexible 0,45. Uniones ocultas sin canto. Base C3-020 a C3-022 conserva cuatro bordes protegidos.</x:v>
       </x:c>
       <x:c r="C15" s="37" t="s">
-        <x:v>286</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="39.599998474121094">
       <x:c r="A16" s="37" t="s">
-        <x:v>287</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B16" s="37" t="s">
-        <x:v>288</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="C16" s="37" t="s">
-        <x:v>289</x:v>
+        <x:v>257</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="100" customHeight="1">
+      <x:c r="A17" t="str">
+        <x:v>Retirada de paneles traseros</x:v>
+      </x:c>
+      <x:c r="B17" s="55" t="str">
+        <x:v>Se retiran C3-005 y C3-011. Pared estucada a la vista, sin panel. Marco perimetral completo: superiores C3-025/C3-026 (830×100 y 1075×100), montantes C3-027/C3-028 (2050×100) e inferiores C3-029/C3-030 (830×100 y 1075×100). RH15; se mantienen divisor, amarres de maletero y bastidor de pino. Anclajes posteriores e izquierdos por dimensionar.</x:v>
+      </x:c>
+      <x:c r="C17" t="str">
+        <x:v>Usuario, 28/10/2026.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
